--- a/data/sensor_configuration_v2.xlsx
+++ b/data/sensor_configuration_v2.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="2880" yWindow="1820" windowWidth="28800" windowHeight="17400" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3300" yWindow="1400" windowWidth="28800" windowHeight="17400" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="sensors" sheetId="1" state="visible" r:id="rId1"/>
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="20">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <color theme="1"/>
@@ -127,12 +127,6 @@
       <sz val="11"/>
     </font>
     <font>
-      <name val="Calibri (Body)"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
       <name val="Calibri"/>
       <family val="2"/>
       <b val="1"/>
@@ -224,7 +218,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -269,7 +263,7 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -279,16 +273,13 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -645,36 +636,36 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="26" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Soil moisture capacitive sensor (such as the DFRobot SEN0308)</t>
         </is>
       </c>
-      <c r="B2" s="26" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Raw Value (ADC)</t>
         </is>
       </c>
-      <c r="C2" s="26" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Raw Sensor Value (ADC)</t>
         </is>
       </c>
-      <c r="D2" s="26" t="inlineStr">
-        <is>
-          <t>Direct sensor reading (digital or analog output)</t>
-        </is>
-      </c>
-      <c r="E2" s="26" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Direct sensor reading (Analog to Digital conversion)</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>air_val_min</t>
         </is>
       </c>
-      <c r="F2" s="26" t="n"/>
-      <c r="G2" s="26" t="n"/>
-      <c r="H2" s="26" t="n"/>
-      <c r="I2" s="26" t="n"/>
-      <c r="J2" s="26" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+      <c r="I2" s="3" t="n"/>
+      <c r="J2" s="3" t="n"/>
       <c r="K2" s="4" t="inlineStr">
         <is>
           <t>kΩ</t>
@@ -687,36 +678,36 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="26" t="n"/>
-      <c r="B3" s="26" t="inlineStr">
+      <c r="A3" s="3" t="n"/>
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Raw Value (%)</t>
         </is>
       </c>
-      <c r="C3" s="26" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Raw Sensor Value (%)</t>
         </is>
       </c>
-      <c r="D3" s="26" t="inlineStr">
-        <is>
-          <t>We will transform the raw value and express it as a percentage - 0% corresponds to the lowest possible value and 100% corresponds to the higest possible value.</t>
-        </is>
-      </c>
-      <c r="E3" s="26" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>We will transform the raw value and express it as a percentage - 0% corresponds to the lowest possible value (dry) and 100% corresponds to the higest possible value (wet).</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>air_val_max</t>
         </is>
       </c>
-      <c r="F3" s="26" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>water_val</t>
         </is>
       </c>
-      <c r="G3" s="26" t="n"/>
-      <c r="H3" s="26" t="n"/>
-      <c r="I3" s="26" t="n"/>
-      <c r="J3" s="26" t="inlineStr">
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+      <c r="I3" s="3" t="n"/>
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>(X-min)/(max-min)*100</t>
         </is>
@@ -733,36 +724,36 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="26" t="n"/>
-      <c r="B4" s="26" t="inlineStr">
+      <c r="A4" s="3" t="n"/>
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Thresholds</t>
         </is>
       </c>
-      <c r="C4" s="26" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Management Thresholds</t>
         </is>
       </c>
-      <c r="D4" s="26" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">This variable will tell you if the soil is very dry, dry or wet. It transforms the raw value into these three qualitative states, using two thresholds that you specify. </t>
         </is>
       </c>
-      <c r="E4" s="26" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="F4" s="26" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>b</t>
         </is>
       </c>
-      <c r="G4" s="26" t="n"/>
-      <c r="H4" s="26" t="n"/>
-      <c r="I4" s="26" t="n"/>
-      <c r="J4" s="26" t="inlineStr">
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+      <c r="I4" s="3" t="n"/>
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>x &gt; a → 'Too a' x &gt; b → 'v ab' → 'good'</t>
         </is>
@@ -775,39 +766,39 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="26" t="n"/>
-      <c r="B5" s="26" t="inlineStr">
+      <c r="A5" s="3" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Wetting Front</t>
         </is>
       </c>
-      <c r="C5" s="26" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Wetting Front arrival at sensor's depth</t>
         </is>
       </c>
-      <c r="D5" s="26" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">This variables specifies when the water has arrived at the depth at which the sensor is positioned. </t>
         </is>
       </c>
-      <c r="E5" s="26" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>shallow</t>
         </is>
       </c>
-      <c r="F5" s="26" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>deep</t>
         </is>
       </c>
-      <c r="G5" s="26" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>threshold</t>
         </is>
       </c>
-      <c r="H5" s="26" t="n"/>
-      <c r="I5" s="26" t="n"/>
+      <c r="H5" s="3" t="n"/>
+      <c r="I5" s="3" t="n"/>
       <c r="J5" s="6" t="n"/>
       <c r="K5" s="5" t="inlineStr">
         <is>
@@ -827,35 +818,35 @@
     </row>
     <row r="6">
       <c r="A6" s="18" t="n"/>
-      <c r="B6" s="26" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>1-2-3 point calibrations</t>
         </is>
       </c>
-      <c r="C6" s="26" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Quick 1, 2 or 3 point calibration procedure</t>
         </is>
       </c>
-      <c r="D6" s="26" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>TO ADD if relevant (not yet implemented)</t>
         </is>
       </c>
-      <c r="E6" s="26" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="F6" s="26" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>b</t>
         </is>
       </c>
-      <c r="G6" s="26" t="n"/>
-      <c r="H6" s="26" t="n"/>
-      <c r="I6" s="26" t="n"/>
-      <c r="J6" s="26" t="inlineStr">
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+      <c r="I6" s="3" t="n"/>
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>soil_moisture-WP*100/(FC-WP)</t>
         </is>
@@ -873,27 +864,27 @@
     </row>
     <row r="7">
       <c r="A7" s="23" t="n"/>
-      <c r="B7" s="26" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Rate of Change of Soil Water Status</t>
         </is>
       </c>
-      <c r="C7" s="26" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Rate of Change</t>
         </is>
       </c>
-      <c r="D7" s="26" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>TO ADD if relevant (not yet implemented)</t>
         </is>
       </c>
-      <c r="E7" s="26" t="n"/>
-      <c r="F7" s="26" t="n"/>
-      <c r="G7" s="26" t="n"/>
-      <c r="H7" s="26" t="n"/>
-      <c r="I7" s="26" t="n"/>
-      <c r="J7" s="26" t="inlineStr">
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+      <c r="I7" s="3" t="n"/>
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>dV/dt = a(good or stop irrigating)</t>
         </is>
@@ -912,43 +903,43 @@
     </row>
     <row r="8">
       <c r="A8" s="24" t="n"/>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Volumetric Soil Moisture</t>
         </is>
       </c>
-      <c r="C8" s="26" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Volumetric Soil Moisture</t>
         </is>
       </c>
-      <c r="D8" s="26" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>The volumetric soil moisture content, expressed here as a percentage (%), references to the volume of water reported to the volume of soil. It is calculated as θv = Vw/Vs⋅100 where Vw is  the water volume, Vs the dry soil volume.</t>
         </is>
       </c>
-      <c r="E8" s="26" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>air_val</t>
         </is>
       </c>
-      <c r="F8" s="26" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>water_val</t>
         </is>
       </c>
-      <c r="G8" s="26" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>FC</t>
         </is>
       </c>
-      <c r="H8" s="26" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>WP</t>
         </is>
       </c>
-      <c r="I8" s="26" t="n"/>
-      <c r="J8" s="26" t="inlineStr">
+      <c r="I8" s="3" t="n"/>
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>1/k*ln(V-water_val)/(air_val-water_val)</t>
         </is>
@@ -967,31 +958,31 @@
     </row>
     <row r="9">
       <c r="A9" s="24" t="n"/>
-      <c r="B9" s="26" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Vertical Flow Rate</t>
         </is>
       </c>
-      <c r="C9" s="26" t="n"/>
-      <c r="D9" s="26" t="n"/>
-      <c r="E9" s="26" t="inlineStr">
+      <c r="C9" s="3" t="n"/>
+      <c r="D9" s="3" t="n"/>
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>shallow</t>
         </is>
       </c>
-      <c r="F9" s="26" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>deep</t>
         </is>
       </c>
-      <c r="G9" s="26" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>threshold</t>
         </is>
       </c>
-      <c r="H9" s="26" t="n"/>
-      <c r="I9" s="26" t="n"/>
-      <c r="J9" s="26" t="n"/>
+      <c r="H9" s="3" t="n"/>
+      <c r="I9" s="3" t="n"/>
+      <c r="J9" s="3" t="n"/>
       <c r="K9" s="8" t="n"/>
       <c r="L9" s="8" t="inlineStr">
         <is>
@@ -1002,43 +993,43 @@
     </row>
     <row r="10">
       <c r="A10" s="24" t="n"/>
-      <c r="B10" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Total Available Water </t>
-        </is>
-      </c>
-      <c r="C10" s="26" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Total Available Water</t>
         </is>
       </c>
-      <c r="D10" s="26" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Total Available Water</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Available water capacity is the amount of water that can be stored in a soil profile and be available for growing crops. It is also known as available water content (AWC), profile available water (PAW) or total available water (TAW).</t>
         </is>
       </c>
-      <c r="E10" s="26" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>air_val</t>
         </is>
       </c>
-      <c r="F10" s="26" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>water_val</t>
         </is>
       </c>
-      <c r="G10" s="26" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>FC</t>
         </is>
       </c>
-      <c r="H10" s="26" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>WP</t>
         </is>
       </c>
-      <c r="I10" s="26" t="n"/>
-      <c r="J10" s="26" t="inlineStr">
+      <c r="I10" s="3" t="n"/>
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>soil_moisture-WP*100/(FC-WP)</t>
         </is>
@@ -1056,32 +1047,32 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="26" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>Irrometer Watermark (200SS)</t>
         </is>
       </c>
-      <c r="B11" s="26" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Raw value (Resistance)</t>
         </is>
       </c>
-      <c r="C11" s="26" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Raw value (Resistance, in kΩ)</t>
         </is>
       </c>
-      <c r="D11" s="26" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>Electrical resistance of the granular matrix, in kilohms. This is only available when the sensor is wired straight to the Arduino. Through the 200SS-VA3 adapter the resistance never leaves the adapter, so on that wiring the reading shown is tension in kPa instead.</t>
         </is>
       </c>
-      <c r="E11" s="26" t="n"/>
-      <c r="F11" s="26" t="n"/>
-      <c r="G11" s="26" t="n"/>
-      <c r="H11" s="26" t="n"/>
-      <c r="I11" s="26" t="n"/>
-      <c r="J11" s="26" t="inlineStr">
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+      <c r="I11" s="3" t="n"/>
+      <c r="J11" s="3" t="inlineStr">
         <is>
           <t>Rx*(Vs-A1)/A1</t>
         </is>
@@ -1098,28 +1089,28 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="26" t="n"/>
-      <c r="B12" s="26" t="inlineStr">
+      <c r="A12" s="3" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Raw Value (%)</t>
         </is>
       </c>
-      <c r="C12" s="26" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>Raw Sensor Value (%)</t>
         </is>
       </c>
-      <c r="D12" s="26" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>This sensor measures electrical resistance inside a granular matrix to determine soil water tension. With this option, you are reading the resistance value (kΩ), expressed as a percentage - 0% corresponds to the lowest possible value and 100% corresponds to the higest possible value.</t>
         </is>
       </c>
-      <c r="E12" s="28" t="inlineStr">
+      <c r="E12" s="26" t="inlineStr">
         <is>
           <t>abs(air_val_max)</t>
         </is>
       </c>
-      <c r="F12" s="28" t="inlineStr">
+      <c r="F12" s="26" t="inlineStr">
         <is>
           <t>water_val</t>
         </is>
@@ -1127,7 +1118,7 @@
       <c r="G12" s="6" t="n"/>
       <c r="H12" s="6" t="n"/>
       <c r="I12" s="6" t="n"/>
-      <c r="J12" s="28" t="inlineStr">
+      <c r="J12" s="26" t="inlineStr">
         <is>
           <t>(X-min)/(max-min)*100</t>
         </is>
@@ -1149,17 +1140,17 @@
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="28" t="inlineStr">
         <is>
           <t>Tension (kPa)</t>
         </is>
       </c>
-      <c r="C13" s="29" t="inlineStr">
+      <c r="C13" s="27" t="inlineStr">
         <is>
           <t>Tension (kPa)</t>
         </is>
       </c>
-      <c r="D13" s="10" t="inlineStr">
+      <c r="D13" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">This sensor measures electrical resistance inside a granular matrix to determine soil water tension. Once resistance is known, a calibration equation converts the value to soil water tension (kPa), using the following equation: kPa = (−3.213 × R − 4.093) / (1 − 0.009733 × R − 0,2892), where R is resistance in kΩ. This covers the range of 10 to 100 kPa. Values are linearly extrapolated for values below 10 kPa and above 100 kPa. You can use this option if you cannot measure soil temperature. </t>
         </is>
@@ -1171,16 +1162,21 @@
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="28" t="inlineStr">
         <is>
           <t>Management Thresholds</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="28" t="inlineStr">
         <is>
           <t>Management Thresholds</t>
         </is>
       </c>
+      <c r="D14" s="28" t="inlineStr">
+        <is>
+          <t>Tells you where the soil stands between (Dry plant stressed, Irrigation range, Saturation).</t>
+        </is>
+      </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
           <t>soil_type</t>
@@ -1203,31 +1199,31 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="26" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Irrometer Watermark (200SS) combined with Irrometer Soil Temperature Sensor (200TS) </t>
         </is>
       </c>
-      <c r="B15" s="26" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Raw value (Resistance)</t>
         </is>
       </c>
-      <c r="C15" s="26" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>Raw value (Resistance, in kΩ)</t>
         </is>
       </c>
-      <c r="D15" s="26" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>Electrical resistance of the granular matrix, in kilohms. This is only available when the sensor is wired straight to the Arduino. Through the 200SS-VA3 adapter the resistance never leaves the adapter, so on that wiring the reading shown is tension in kPa instead.</t>
         </is>
       </c>
-      <c r="E15" s="26" t="n"/>
-      <c r="F15" s="26" t="n"/>
-      <c r="G15" s="26" t="n"/>
-      <c r="H15" s="26" t="n"/>
-      <c r="I15" s="26" t="n"/>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n"/>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+      <c r="I15" s="3" t="n"/>
       <c r="J15" s="11" t="inlineStr">
         <is>
           <t>Rx*(Vs-A1)/A1</t>
@@ -1245,28 +1241,28 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="26" t="n"/>
-      <c r="B16" s="26" t="inlineStr">
+      <c r="A16" s="3" t="n"/>
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Raw Value (%)</t>
         </is>
       </c>
-      <c r="C16" s="28" t="inlineStr">
+      <c r="C16" s="26" t="inlineStr">
         <is>
           <t>Raw Sensor Value (%)</t>
         </is>
       </c>
-      <c r="D16" s="26" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>This sensor measures electrical resistance inside a granular matrix to determine soil water tension. With this option, you are reading the resistance value (kΩ), expressed as a percentage - 0% corresponds to the lowest possible value and 100% corresponds to the higest possible value.</t>
         </is>
       </c>
-      <c r="E16" s="28" t="inlineStr">
+      <c r="E16" s="26" t="inlineStr">
         <is>
           <t>abs(air_val_max)</t>
         </is>
       </c>
-      <c r="F16" s="28" t="inlineStr">
+      <c r="F16" s="26" t="inlineStr">
         <is>
           <t>water_val</t>
         </is>
@@ -1274,7 +1270,7 @@
       <c r="G16" s="6" t="n"/>
       <c r="H16" s="6" t="n"/>
       <c r="I16" s="6" t="n"/>
-      <c r="J16" s="28" t="inlineStr">
+      <c r="J16" s="26" t="inlineStr">
         <is>
           <t>(X-min)/(max-min)*100</t>
         </is>
@@ -1296,28 +1292,28 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="26" t="n"/>
-      <c r="B17" s="26" t="inlineStr">
+      <c r="A17" s="3" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Tension</t>
         </is>
       </c>
-      <c r="C17" s="28" t="inlineStr">
+      <c r="C17" s="26" t="inlineStr">
         <is>
           <t>Tension</t>
         </is>
       </c>
-      <c r="D17" s="26" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">This sensor measures electrical resistance inside a granular matrix to determine soil water tension. Once resistance is known, a calibration equation converts the value to soil water tension (kPa), using the following equation: kPa = (−3.213 × R − 4.093) / (1 − 0.009733 × R − 0.01205 × T), where R is resistance in kΩ and T is temperature in °C. This covers the range of 10 to 100 kPa. Values are linearly extrapolated for values below 10 kPa and above 100 kPa. Temperature affects the measured resistance; a temperature sensor input improves accuracy. . You can use this option if you can measure soil temperature. </t>
         </is>
       </c>
-      <c r="E17" s="26" t="n"/>
-      <c r="F17" s="26" t="n"/>
-      <c r="G17" s="26" t="n"/>
-      <c r="H17" s="26" t="n"/>
-      <c r="I17" s="26" t="n"/>
-      <c r="J17" s="26" t="inlineStr">
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="3" t="n"/>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+      <c r="I17" s="3" t="n"/>
+      <c r="J17" s="3" t="inlineStr">
         <is>
           <t>Inside of the code itself for simplicity</t>
         </is>
@@ -1334,28 +1330,28 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="26" t="n"/>
-      <c r="B18" s="26" t="inlineStr">
+      <c r="A18" s="3" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Raw value (Temperature, in °F)</t>
         </is>
       </c>
-      <c r="C18" s="26" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>Raw value (Temperature, in °F)</t>
         </is>
       </c>
-      <c r="D18" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">You are reading soil temperature using your soil temperature sensor. </t>
-        </is>
-      </c>
-      <c r="E18" s="26" t="n"/>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You are reading soil temperature in Fahrenheit using your soil temperature sensor. </t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n"/>
       <c r="F18" s="25" t="n"/>
-      <c r="G18" s="26" t="n"/>
-      <c r="H18" s="26" t="n"/>
-      <c r="I18" s="28" t="n"/>
-      <c r="J18" s="26" t="inlineStr">
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
+      <c r="I18" s="26" t="n"/>
+      <c r="J18" s="3" t="inlineStr">
         <is>
           <t>20 + 48.48(V-0.49)</t>
         </is>
@@ -1377,28 +1373,28 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="26" t="n"/>
-      <c r="B19" s="26" t="inlineStr">
+      <c r="A19" s="3" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Raw value (Temperature, in °C)</t>
         </is>
       </c>
-      <c r="C19" s="26" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>Raw value (Temperature, in °C)</t>
         </is>
       </c>
-      <c r="D19" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">You are reading soil temperature using your soil temperature sensor. </t>
-        </is>
-      </c>
-      <c r="E19" s="26" t="n"/>
-      <c r="F19" s="26" t="n"/>
-      <c r="G19" s="26" t="n"/>
-      <c r="H19" s="26" t="n"/>
-      <c r="I19" s="26" t="n"/>
-      <c r="J19" s="26" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You are reading soil temperature in Celsius using your soil temperature sensor. </t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="n"/>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+      <c r="I19" s="3" t="n"/>
+      <c r="J19" s="3" t="inlineStr">
         <is>
           <t>((20+48.48(V-0.49)-32)/1.8)</t>
         </is>
@@ -1459,22 +1455,22 @@
           <t>Irrometer Soil Temperature Sensor (200TS)</t>
         </is>
       </c>
-      <c r="B21" s="26" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Raw value (Temperature, in °F)</t>
         </is>
       </c>
-      <c r="C21" s="26" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>Raw value (Temperature, in °F)</t>
         </is>
       </c>
-      <c r="D21" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">You are reading soil temperature using your soil temperature sensor. </t>
-        </is>
-      </c>
-      <c r="J21" s="26" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You are reading soil temperature in Fahrenheit using your soil temperature sensor. </t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
         <is>
           <t>20 + 48.48(V-0.49)</t>
         </is>
@@ -1492,22 +1488,22 @@
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="12" t="n"/>
-      <c r="B22" s="26" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Raw value (Temperature, in °C)</t>
         </is>
       </c>
-      <c r="C22" s="26" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>Raw value (Temperature, in °C)</t>
         </is>
       </c>
-      <c r="D22" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">You are reading soil temperature using your soil temperature sensor. </t>
-        </is>
-      </c>
-      <c r="J22" s="26" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You are reading soil temperature in Celsius using your soil temperature sensor. </t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
         <is>
           <t>((20+48.48(V-0.49)-32)/1.8)</t>
         </is>
@@ -2579,33 +2575,33 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="26" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>DF_robot</t>
         </is>
       </c>
-      <c r="B2" s="26" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>air_val</t>
         </is>
       </c>
-      <c r="C2" s="26" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Air value</t>
         </is>
       </c>
-      <c r="D2" s="26" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Air value: raw reading in open air. The DFRobot probe outputs at most 2.9 V, about 593 counts on a 5 V board, so this sits just under 600.</t>
         </is>
       </c>
-      <c r="E2" s="26" t="n">
+      <c r="E2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F2" s="26" t="n">
+      <c r="F2" s="3" t="n">
         <v>1023</v>
       </c>
-      <c r="G2" s="26" t="n">
+      <c r="G2" s="3" t="n">
         <v>590</v>
       </c>
       <c r="H2" s="5" t="inlineStr">
@@ -2615,33 +2611,33 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="26" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>DF_robot</t>
         </is>
       </c>
-      <c r="B3" s="26" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>water_val</t>
         </is>
       </c>
-      <c r="C3" s="26" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Water value</t>
         </is>
       </c>
-      <c r="D3" s="26" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Water value: raw reading submerged in water</t>
         </is>
       </c>
-      <c r="E3" s="26" t="n">
+      <c r="E3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F3" s="26" t="n">
+      <c r="F3" s="3" t="n">
         <v>1023</v>
       </c>
-      <c r="G3" s="26" t="n">
+      <c r="G3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H3" s="5" t="inlineStr">
@@ -2651,33 +2647,33 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="26" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>DF_robot</t>
         </is>
       </c>
-      <c r="B4" s="26" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>fc</t>
         </is>
       </c>
-      <c r="C4" s="26" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Field Capacity</t>
         </is>
       </c>
-      <c r="D4" s="26" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Field capacity: The amount of water that remains in the soil after all the excess water at saturation has been drained.</t>
         </is>
       </c>
-      <c r="E4" s="26" t="n">
+      <c r="E4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="26" t="n">
+      <c r="F4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G4" s="26" t="n">
+      <c r="G4" s="3" t="n">
         <v>0.3</v>
       </c>
       <c r="H4" s="5" t="inlineStr">
@@ -2687,33 +2683,33 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="26" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>DF_robot</t>
         </is>
       </c>
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>wp</t>
         </is>
       </c>
-      <c r="C5" s="26" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Wilting point</t>
         </is>
       </c>
-      <c r="D5" s="26" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Wilting point:  When plants take up all the available water for a given soil and it dries out to the point where it cannot supply any water to keep plants from dying </t>
         </is>
       </c>
-      <c r="E5" s="26" t="n">
+      <c r="E5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="26" t="n">
+      <c r="F5" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="26" t="n">
+      <c r="G5" s="3" t="n">
         <v>0.1</v>
       </c>
       <c r="H5" s="5" t="inlineStr">
@@ -2723,74 +2719,74 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="26" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>DF_robot</t>
         </is>
       </c>
-      <c r="B6" s="26" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>k</t>
         </is>
       </c>
-      <c r="C6" s="26" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>k</t>
         </is>
       </c>
-      <c r="D6" s="26" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>k: calibration scaling factor, fitted by matching gravimetric samples to the sensor. The default spreads a typical probe across 0 to about 50 % volumetric water, but it is soil specific and should be calibrated.</t>
         </is>
       </c>
-      <c r="E6" s="26" t="n">
+      <c r="E6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="26" t="n">
+      <c r="F6" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="G6" s="26" t="n">
+      <c r="G6" s="3" t="n">
         <v>2.2</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="n"/>
-      <c r="B7" s="10" t="n"/>
-      <c r="C7" s="10" t="n"/>
-      <c r="D7" s="10" t="n"/>
-      <c r="E7" s="10" t="n"/>
-      <c r="F7" s="10" t="n"/>
-      <c r="G7" s="10" t="n"/>
+      <c r="A7" s="28" t="n"/>
+      <c r="B7" s="28" t="n"/>
+      <c r="C7" s="28" t="n"/>
+      <c r="D7" s="28" t="n"/>
+      <c r="E7" s="28" t="n"/>
+      <c r="F7" s="28" t="n"/>
+      <c r="G7" s="28" t="n"/>
       <c r="H7" s="5" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="28" t="inlineStr">
         <is>
           <t>Watermark</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="28" t="inlineStr">
         <is>
           <t>water_val</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="28" t="inlineStr">
         <is>
           <t>Water value</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="28" t="inlineStr">
         <is>
           <t>Water value: raw reading submerged in water</t>
         </is>
       </c>
-      <c r="E8" s="10" t="n">
+      <c r="E8" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="10" t="n">
+      <c r="F8" s="28" t="n">
         <v>239</v>
       </c>
-      <c r="G8" s="10" t="n">
+      <c r="G8" s="28" t="n">
         <v>0</v>
       </c>
       <c r="H8" s="14" t="inlineStr">
@@ -2800,33 +2796,33 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="28" t="inlineStr">
         <is>
           <t>Watermark</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="28" t="inlineStr">
         <is>
           <t>Resistance</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C9" s="28" t="inlineStr">
         <is>
           <t>Resistance</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="D9" s="28" t="inlineStr">
         <is>
           <t>Resistance</t>
         </is>
       </c>
-      <c r="E9" s="10" t="n">
+      <c r="E9" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="10" t="n">
+      <c r="F9" s="28" t="n">
         <v>200</v>
       </c>
-      <c r="G9" s="10" t="n">
+      <c r="G9" s="28" t="n">
         <v>0</v>
       </c>
       <c r="H9" s="14" t="inlineStr">
@@ -2836,33 +2832,33 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="26" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>DF_robot</t>
         </is>
       </c>
-      <c r="B10" s="26" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>air_val_min</t>
         </is>
       </c>
-      <c r="C10" s="26" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Air value (minimum)</t>
         </is>
       </c>
-      <c r="D10" s="26" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Air value: raw reading in open air</t>
         </is>
       </c>
-      <c r="E10" s="26" t="n">
+      <c r="E10" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="26" t="n">
+      <c r="F10" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="26" t="n">
+      <c r="G10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H10" s="5" t="inlineStr">
@@ -2872,7 +2868,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="26" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>DF_robot</t>
         </is>
@@ -2908,7 +2904,7 @@
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="28" t="inlineStr">
         <is>
           <t>DF_robot</t>
         </is>
@@ -2939,7 +2935,7 @@
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="28" t="inlineStr">
         <is>
           <t>DF_robot</t>
         </is>
@@ -2970,7 +2966,7 @@
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="28" t="inlineStr">
         <is>
           <t>DF_robot</t>
         </is>
@@ -3001,7 +2997,7 @@
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="28" t="inlineStr">
         <is>
           <t>DF_robot</t>
         </is>
@@ -3032,7 +3028,7 @@
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="28" t="inlineStr">
         <is>
           <t>DF_robot</t>
         </is>
@@ -3063,7 +3059,7 @@
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="28" t="inlineStr">
         <is>
           <t>Watermark</t>
         </is>
@@ -3094,7 +3090,7 @@
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="28" t="inlineStr">
         <is>
           <t>Watermark_Temperature</t>
         </is>
@@ -3125,7 +3121,7 @@
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="28" t="inlineStr">
         <is>
           <t>Watermark_Temperature</t>
         </is>
@@ -3156,7 +3152,7 @@
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="A20" s="28" t="inlineStr">
         <is>
           <t>Watermark</t>
         </is>
@@ -3188,7 +3184,7 @@
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="A21" s="28" t="inlineStr">
         <is>
           <t>Watermark_Temperature</t>
         </is>
@@ -3220,7 +3216,7 @@
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="A22" s="28" t="inlineStr">
         <is>
           <t>Watermark</t>
         </is>
@@ -3251,7 +3247,7 @@
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="A23" s="28" t="inlineStr">
         <is>
           <t>Watermark</t>
         </is>
@@ -3282,7 +3278,7 @@
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="A24" s="28" t="inlineStr">
         <is>
           <t>Watermark_Temperature</t>
         </is>
@@ -3313,7 +3309,7 @@
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="A25" s="28" t="inlineStr">
         <is>
           <t>Watermark_Temperature</t>
         </is>
@@ -3364,14 +3360,11 @@
           <t>How the sensor reaches the board. Through the 200SS-VA3 adapter, which does the excitation and calibration itself, or wired straight to the Arduino with a series resistor. Direct wiring supports one Watermark only: two bare sensors in the same soil read through each other and damage their electrodes.</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>200SS-VA3 adapter</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>200SS-VA3 adapter|Direct to Arduino</t>
@@ -3435,14 +3428,11 @@
           <t>How the sensor reaches the board. Through the 200SS-VA3 adapter, which does the excitation and calibration itself, or wired straight to the Arduino with a series resistor. Direct wiring supports one Watermark only: two bare sensors in the same soil read through each other and damage their electrodes.</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>200SS-VA3 adapter</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>200SS-VA3 adapter|Direct to Arduino</t>
@@ -3506,14 +3496,11 @@
           <t>How the sensor reaches the board. Through the 200SS-VA3 adapter, which does the excitation and calibration itself, or wired straight to the Arduino with a series resistor. Direct wiring supports one Watermark only: two bare sensors in the same soil read through each other and damage their electrodes.</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>200SS-VA3 adapter</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>200SS-VA3 adapter|Direct to Arduino</t>
@@ -4681,135 +4668,135 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="26" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>filename</t>
         </is>
       </c>
-      <c r="B2" s="26" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>File name</t>
         </is>
       </c>
-      <c r="C2" s="26" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="D2" s="26" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="E2" s="26" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>e.g. apples_field2 (no spaces, no .ino)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="26" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B3" s="26" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Your name</t>
         </is>
       </c>
-      <c r="C3" s="26" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="D3" s="26" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="E3" s="26" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>e.g. John R.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="26" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>country</t>
         </is>
       </c>
-      <c r="B4" s="26" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="C4" s="26" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="D4" s="26" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="E4" s="26" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>e.g. United States of America</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="26" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Email address</t>
         </is>
       </c>
-      <c r="C5" s="26" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="D5" s="26" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="E5" s="26" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>e.g. name@example.com</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="26" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>ino_comment</t>
         </is>
       </c>
-      <c r="B6" s="26" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Comment to include in the code (optional)</t>
         </is>
       </c>
-      <c r="C6" s="26" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="D6" s="26" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="E6" s="26" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>e.g. Orchard block 2, installed June 2026</t>
         </is>
@@ -5807,7 +5794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5826,6 +5813,11 @@
           <t>port_tip</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>active (TRUE/FALSE)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5835,7 +5827,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Analog pin A1. A0 is taken by the shield's buttons, so sensors start at A1.</t>
+          <t>Analog pin A1. A0 is taken by the shield's buttons, so sensors start here.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
@@ -5850,6 +5847,11 @@
           <t>Analog pin A2.</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5862,6 +5864,11 @@
           <t>Analog pin A3.</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5874,6 +5881,11 @@
           <t>Analog pin A4.</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5884,6 +5896,232 @@
       <c r="B6" t="inlineStr">
         <is>
           <t>Analog pin A5.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Digital pin 1. Shared with the USB serial line: using it breaks uploads and the serial monitor.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Digital pin 2. Free on the shield, currently used as a direct-wiring excitation pin.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Digital pin 3. Free on the shield, currently used as a direct-wiring excitation pin.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Digital pin 4. Used by the LCD keypad shield.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>D5</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Digital pin 5. Used by the LCD keypad shield.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>D6</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Digital pin 6. Used by the LCD keypad shield.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>D7</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Digital pin 7. Used by the LCD keypad shield.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>D8</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Digital pin 8. Used by the LCD keypad shield.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>D9</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Digital pin 9. Used by the LCD keypad shield.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>D10</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Digital pin 10. Drives the LCD backlight.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>D11</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Digital pin 11. Free on the shield.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>D12</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Digital pin 12. Free on the shield.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>D13</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Digital pin 13. Free, but shares the onboard LED.</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
@@ -6912,145 +7150,145 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="26" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="B2" s="26" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>No visualization</t>
         </is>
       </c>
-      <c r="C2" s="26" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Display the information in a visual representation on the LCD screen. Currently there is nothing selected.</t>
         </is>
       </c>
-      <c r="D2" s="26" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="26" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>bar</t>
         </is>
       </c>
-      <c r="B3" s="26" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Loading bar</t>
         </is>
       </c>
-      <c r="C3" s="26" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Displays a loading bar that changes based on water content.</t>
         </is>
       </c>
-      <c r="D3" s="26" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="26" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>raw_lcd</t>
         </is>
       </c>
-      <c r="B4" s="26" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Raw value</t>
         </is>
       </c>
-      <c r="C4" s="26" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Displays the raw sensor value</t>
         </is>
       </c>
-      <c r="D4" s="26" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="26" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>state_lcd</t>
         </is>
       </c>
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>State: Very Dry, Dry, or Wet</t>
         </is>
       </c>
-      <c r="C5" s="26" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Displays the general state at which soil seems to be for the capacitive sensors</t>
         </is>
       </c>
-      <c r="D5" s="26" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="26" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>transformed_lcd</t>
         </is>
       </c>
-      <c r="B6" s="26" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Transformed Raw Value 0-100</t>
         </is>
       </c>
-      <c r="C6" s="26" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>A more concise version of the raw sensor value</t>
         </is>
       </c>
-      <c r="D6" s="26" t="b">
+      <c r="D6" s="3" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="26" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>rate</t>
         </is>
       </c>
-      <c r="B7" s="26" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Rate of change (future)</t>
         </is>
       </c>
-      <c r="C7" s="26" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>The change in available water over time</t>
         </is>
       </c>
-      <c r="D7" s="26" t="b">
+      <c r="D7" s="3" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="28" t="inlineStr">
         <is>
           <t>front_lcd</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="28" t="inlineStr">
         <is>
           <t>Front detected</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="28" t="inlineStr">
         <is>
           <t>Shows front detected when the wetting front reaches the deep sensor</t>
         </is>
@@ -7060,17 +7298,17 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="28" t="inlineStr">
         <is>
           <t>temp_lcd</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="28" t="inlineStr">
         <is>
           <t>Temperature</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C9" s="28" t="inlineStr">
         <is>
           <t>Displays the temperatue in celsius</t>
         </is>
@@ -7082,17 +7320,17 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="28" t="inlineStr">
         <is>
           <t>kpa_lcd</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="28" t="inlineStr">
         <is>
           <t>Tension</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="28" t="inlineStr">
         <is>
           <t>Displays soil tension in kPa</t>
         </is>
@@ -7102,17 +7340,17 @@
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="28" t="inlineStr">
         <is>
           <t>rate_lcd</t>
         </is>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="28" t="inlineStr">
         <is>
           <t>Flow rate</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="28" t="inlineStr">
         <is>
           <t>Displays the flow rate between 2 sensors</t>
         </is>
@@ -7124,17 +7362,17 @@
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="28" t="inlineStr">
         <is>
           <t>wm_state_lcd</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>State: Dry plant stressed, Irrigation range, or Saturation</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="28" t="inlineStr">
         <is>
           <t>Displays the state at which the soils seems to be for the Watermark sensors</t>
         </is>

--- a/data/sensor_configuration_v2.xlsx
+++ b/data/sensor_configuration_v2.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3300" yWindow="1400" windowWidth="28800" windowHeight="17400" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="600" windowWidth="28800" windowHeight="17400" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="sensors" sheetId="1" state="visible" r:id="rId1"/>
@@ -218,7 +218,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -277,9 +277,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -995,7 +992,7 @@
       <c r="A10" s="24" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Total Available Water</t>
+          <t xml:space="preserve">Total Available Water </t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -1140,7 +1137,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="28" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>Tension (kPa)</t>
         </is>
@@ -1150,7 +1147,7 @@
           <t>Tension (kPa)</t>
         </is>
       </c>
-      <c r="D13" s="28" t="inlineStr">
+      <c r="D13" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">This sensor measures electrical resistance inside a granular matrix to determine soil water tension. Once resistance is known, a calibration equation converts the value to soil water tension (kPa), using the following equation: kPa = (−3.213 × R − 4.093) / (1 − 0.009733 × R − 0,2892), where R is resistance in kΩ. This covers the range of 10 to 100 kPa. Values are linearly extrapolated for values below 10 kPa and above 100 kPa. You can use this option if you cannot measure soil temperature. </t>
         </is>
@@ -1162,17 +1159,17 @@
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
-      <c r="B14" s="28" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>Management Thresholds</t>
         </is>
       </c>
-      <c r="C14" s="28" t="inlineStr">
+      <c r="C14" s="10" t="inlineStr">
         <is>
           <t>Management Thresholds</t>
         </is>
       </c>
-      <c r="D14" s="28" t="inlineStr">
+      <c r="D14" s="10" t="inlineStr">
         <is>
           <t>Tells you where the soil stands between (Dry plant stressed, Irrigation range, Saturation).</t>
         </is>
@@ -2750,43 +2747,43 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="28" t="n"/>
-      <c r="B7" s="28" t="n"/>
-      <c r="C7" s="28" t="n"/>
-      <c r="D7" s="28" t="n"/>
-      <c r="E7" s="28" t="n"/>
-      <c r="F7" s="28" t="n"/>
-      <c r="G7" s="28" t="n"/>
+      <c r="A7" s="10" t="n"/>
+      <c r="B7" s="10" t="n"/>
+      <c r="C7" s="10" t="n"/>
+      <c r="D7" s="10" t="n"/>
+      <c r="E7" s="10" t="n"/>
+      <c r="F7" s="10" t="n"/>
+      <c r="G7" s="10" t="n"/>
       <c r="H7" s="5" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="28" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>Watermark</t>
         </is>
       </c>
-      <c r="B8" s="28" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>water_val</t>
         </is>
       </c>
-      <c r="C8" s="28" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>Water value</t>
         </is>
       </c>
-      <c r="D8" s="28" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>Water value: raw reading submerged in water</t>
         </is>
       </c>
-      <c r="E8" s="28" t="n">
+      <c r="E8" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="28" t="n">
+      <c r="F8" s="10" t="n">
         <v>239</v>
       </c>
-      <c r="G8" s="28" t="n">
+      <c r="G8" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H8" s="14" t="inlineStr">
@@ -2796,33 +2793,33 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="28" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>Watermark</t>
         </is>
       </c>
-      <c r="B9" s="28" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>Resistance</t>
         </is>
       </c>
-      <c r="C9" s="28" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>Resistance</t>
         </is>
       </c>
-      <c r="D9" s="28" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>Resistance</t>
         </is>
       </c>
-      <c r="E9" s="28" t="n">
+      <c r="E9" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="28" t="n">
+      <c r="F9" s="10" t="n">
         <v>200</v>
       </c>
-      <c r="G9" s="28" t="n">
+      <c r="G9" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H9" s="14" t="inlineStr">
@@ -2904,7 +2901,7 @@
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
-      <c r="A12" s="28" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>DF_robot</t>
         </is>
@@ -2935,7 +2932,7 @@
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
-      <c r="A13" s="28" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>DF_robot</t>
         </is>
@@ -2966,7 +2963,7 @@
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
-      <c r="A14" s="28" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>DF_robot</t>
         </is>
@@ -2997,7 +2994,7 @@
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="28" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>DF_robot</t>
         </is>
@@ -3028,7 +3025,7 @@
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
-      <c r="A16" s="28" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>DF_robot</t>
         </is>
@@ -3059,7 +3056,7 @@
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="28" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>Watermark</t>
         </is>
@@ -3090,7 +3087,7 @@
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
-      <c r="A18" s="28" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>Watermark_Temperature</t>
         </is>
@@ -3121,7 +3118,7 @@
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="28" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>Watermark_Temperature</t>
         </is>
@@ -3152,7 +3149,7 @@
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="28" t="inlineStr">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t>Watermark</t>
         </is>
@@ -3184,7 +3181,7 @@
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="28" t="inlineStr">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>Watermark_Temperature</t>
         </is>
@@ -3216,7 +3213,7 @@
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="28" t="inlineStr">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>Watermark</t>
         </is>
@@ -3247,7 +3244,7 @@
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="28" t="inlineStr">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>Watermark</t>
         </is>
@@ -3278,7 +3275,7 @@
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="28" t="inlineStr">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>Watermark_Temperature</t>
         </is>
@@ -3309,7 +3306,7 @@
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="28" t="inlineStr">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>Watermark_Temperature</t>
         </is>
@@ -7278,17 +7275,17 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="28" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>front_lcd</t>
         </is>
       </c>
-      <c r="B8" s="28" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>Front detected</t>
         </is>
       </c>
-      <c r="C8" s="28" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>Shows front detected when the wetting front reaches the deep sensor</t>
         </is>
@@ -7298,17 +7295,17 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="28" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>temp_lcd</t>
         </is>
       </c>
-      <c r="B9" s="28" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>Temperature</t>
         </is>
       </c>
-      <c r="C9" s="28" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>Displays the temperatue in celsius</t>
         </is>
@@ -7320,17 +7317,17 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="28" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>kpa_lcd</t>
         </is>
       </c>
-      <c r="B10" s="28" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>Tension</t>
         </is>
       </c>
-      <c r="C10" s="28" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>Displays soil tension in kPa</t>
         </is>
@@ -7340,17 +7337,17 @@
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
-      <c r="A11" s="28" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>rate_lcd</t>
         </is>
       </c>
-      <c r="B11" s="28" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>Flow rate</t>
         </is>
       </c>
-      <c r="C11" s="28" t="inlineStr">
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>Displays the flow rate between 2 sensors</t>
         </is>
@@ -7362,17 +7359,17 @@
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
-      <c r="A12" s="28" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>wm_state_lcd</t>
         </is>
       </c>
-      <c r="B12" s="28" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>State: Dry plant stressed, Irrigation range, or Saturation</t>
         </is>
       </c>
-      <c r="C12" s="28" t="inlineStr">
+      <c r="C12" s="10" t="inlineStr">
         <is>
           <t>Displays the state at which the soils seems to be for the Watermark sensors</t>
         </is>

--- a/data/sensor_configuration_v2.xlsx
+++ b/data/sensor_configuration_v2.xlsx
@@ -992,7 +992,7 @@
       <c r="A10" s="24" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Total Available Water </t>
+          <t>Total Available Water</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -1198,7 +1198,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Irrometer Watermark (200SS) combined with Irrometer Soil Temperature Sensor (200TS) </t>
+          <t>Irrometer Watermark (200SS) combined with Irrometer Soil Temperature Sensor (200TS)</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">

--- a/data/sensor_configuration_v2.xlsx
+++ b/data/sensor_configuration_v2.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="600" windowWidth="28800" windowHeight="17400" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="1360" yWindow="5620" windowWidth="28800" windowHeight="17400" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="sensors" sheetId="1" state="visible" r:id="rId1"/>
@@ -218,7 +218,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -277,6 +277,12 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1179,12 +1185,12 @@
           <t>soil_type</t>
         </is>
       </c>
-      <c r="F14" s="16" t="inlineStr">
+      <c r="F14" s="29" t="inlineStr">
         <is>
           <t>thr_low</t>
         </is>
       </c>
-      <c r="G14" s="16" t="inlineStr">
+      <c r="G14" s="29" t="inlineStr">
         <is>
           <t>thr_high</t>
         </is>
@@ -2514,7 +2520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="3"/>
@@ -2625,7 +2631,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Water value: raw reading submerged in water</t>
+          <t>Water value: the raw reading with the probe standing in water. Typically around 280 on a 5 V board. Measure it, do not assume it.</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
@@ -2635,7 +2641,7 @@
         <v>1023</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
@@ -2743,7 +2749,7 @@
         <v>10</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>2.2</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="7">
@@ -2788,43 +2794,43 @@
       </c>
       <c r="H8" s="14" t="inlineStr">
         <is>
-          <t>kΩ</t>
+          <t>kPa</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>Watermark</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>Resistance</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>Resistance</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="inlineStr">
-        <is>
-          <t>Resistance</t>
-        </is>
-      </c>
-      <c r="E9" s="10" t="n">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>DF_robot</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>air_val_min</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Air value (minimum)</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Air value: raw reading in open air</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="10" t="n">
-        <v>200</v>
-      </c>
-      <c r="G9" s="10" t="n">
+      <c r="F9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="14" t="inlineStr">
-        <is>
-          <t>kΩ</t>
+      <c r="G9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>ADC</t>
         </is>
       </c>
     </row>
@@ -2834,67 +2840,67 @@
           <t>DF_robot</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>air_val_min</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Air value (minimum)</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>air_val_max</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>Air value (max)</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
         <is>
           <t>Air value: raw reading in open air</t>
         </is>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="E10" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="3" t="n">
+      <c r="F10" s="15" t="n">
+        <v>1023</v>
+      </c>
+      <c r="G10" s="15" t="n">
+        <v>590</v>
+      </c>
+      <c r="H10" s="14" t="inlineStr">
+        <is>
+          <t>ADC</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>DF_robot</t>
+        </is>
+      </c>
+      <c r="B11" s="28" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="C11" s="28" t="inlineStr">
+        <is>
+          <t>Upper threshold</t>
+        </is>
+      </c>
+      <c r="D11" s="28" t="inlineStr">
+        <is>
+          <t>The upper threshold used to calculate the state of the sensor.</t>
+        </is>
+      </c>
+      <c r="E11" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>ADC</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>DF_robot</t>
-        </is>
-      </c>
-      <c r="B11" s="15" t="inlineStr">
-        <is>
-          <t>air_val_max</t>
-        </is>
-      </c>
-      <c r="C11" s="15" t="inlineStr">
-        <is>
-          <t>Air value (max)</t>
-        </is>
-      </c>
-      <c r="D11" s="15" t="inlineStr">
-        <is>
-          <t>Air value: raw reading in open air</t>
-        </is>
-      </c>
-      <c r="E11" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="15" t="n">
+      <c r="F11" s="28" t="n">
         <v>1023</v>
       </c>
-      <c r="G11" s="15" t="n">
-        <v>600</v>
-      </c>
-      <c r="H11" s="14" t="inlineStr">
+      <c r="G11" s="28" t="n">
+        <v>450</v>
+      </c>
+      <c r="H11" s="20" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
@@ -2906,24 +2912,29 @@
           <t>DF_robot</t>
         </is>
       </c>
-      <c r="B12" s="19" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="C12" s="19" t="inlineStr">
-        <is>
-          <t>Upper threshold</t>
-        </is>
-      </c>
-      <c r="E12" s="19" t="n">
+      <c r="B12" s="28" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="C12" s="28" t="inlineStr">
+        <is>
+          <t>Lower threshold</t>
+        </is>
+      </c>
+      <c r="D12" s="28" t="inlineStr">
+        <is>
+          <t>The lower theshold used to calculate the state of the sensor.</t>
+        </is>
+      </c>
+      <c r="E12" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="19" t="n">
+      <c r="F12" s="28" t="n">
         <v>1023</v>
       </c>
-      <c r="G12" s="19" t="n">
-        <v>450</v>
+      <c r="G12" s="28" t="n">
+        <v>350</v>
       </c>
       <c r="H12" s="20" t="inlineStr">
         <is>
@@ -2937,28 +2948,33 @@
           <t>DF_robot</t>
         </is>
       </c>
-      <c r="B13" s="19" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
-      <c r="C13" s="19" t="inlineStr">
-        <is>
-          <t>Lower threshold</t>
-        </is>
-      </c>
-      <c r="E13" s="19" t="n">
+      <c r="B13" s="28" t="inlineStr">
+        <is>
+          <t>shallow</t>
+        </is>
+      </c>
+      <c r="C13" s="28" t="inlineStr">
+        <is>
+          <t>Shallow sensor depth</t>
+        </is>
+      </c>
+      <c r="D13" s="28" t="inlineStr">
+        <is>
+          <t>The depth of the sensor closest to the surface.</t>
+        </is>
+      </c>
+      <c r="E13" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="19" t="n">
-        <v>1023</v>
-      </c>
-      <c r="G13" s="19" t="n">
-        <v>350</v>
+      <c r="F13" s="28" t="n">
+        <v>200</v>
+      </c>
+      <c r="G13" s="28" t="n">
+        <v>15</v>
       </c>
       <c r="H13" s="20" t="inlineStr">
         <is>
-          <t>ADC</t>
+          <t>cm</t>
         </is>
       </c>
     </row>
@@ -2968,24 +2984,29 @@
           <t>DF_robot</t>
         </is>
       </c>
-      <c r="B14" s="19" t="inlineStr">
-        <is>
-          <t>shallow</t>
-        </is>
-      </c>
-      <c r="C14" s="19" t="inlineStr">
-        <is>
-          <t>Shallow sensor depth</t>
-        </is>
-      </c>
-      <c r="E14" s="19" t="n">
+      <c r="B14" s="28" t="inlineStr">
+        <is>
+          <t>deep</t>
+        </is>
+      </c>
+      <c r="C14" s="28" t="inlineStr">
+        <is>
+          <t>Deep sensor depth</t>
+        </is>
+      </c>
+      <c r="D14" s="28" t="inlineStr">
+        <is>
+          <t>The depth of the sensor deepest in the soil.</t>
+        </is>
+      </c>
+      <c r="E14" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="F14" s="19" t="n">
+      <c r="F14" s="28" t="n">
         <v>200</v>
       </c>
-      <c r="G14" s="19" t="n">
-        <v>15</v>
+      <c r="G14" s="28" t="n">
+        <v>40</v>
       </c>
       <c r="H14" s="20" t="inlineStr">
         <is>
@@ -2999,85 +3020,100 @@
           <t>DF_robot</t>
         </is>
       </c>
-      <c r="B15" s="19" t="inlineStr">
-        <is>
-          <t>deep</t>
-        </is>
-      </c>
-      <c r="C15" s="19" t="inlineStr">
-        <is>
-          <t>Deep sensor depth</t>
-        </is>
-      </c>
-      <c r="E15" s="19" t="n">
+      <c r="B15" s="28" t="inlineStr">
+        <is>
+          <t>threshold</t>
+        </is>
+      </c>
+      <c r="C15" s="28" t="inlineStr">
+        <is>
+          <t>Front arrival reading</t>
+        </is>
+      </c>
+      <c r="D15" s="28" t="inlineStr">
+        <is>
+          <t>The threshold for the front arrival.</t>
+        </is>
+      </c>
+      <c r="E15" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="F15" s="19" t="n">
-        <v>200</v>
-      </c>
-      <c r="G15" s="19" t="n">
-        <v>40</v>
-      </c>
-      <c r="H15" s="20" t="inlineStr">
-        <is>
-          <t>cm</t>
+      <c r="F15" s="28" t="n">
+        <v>1023</v>
+      </c>
+      <c r="G15" s="28" t="n">
+        <v>400</v>
+      </c>
+      <c r="H15" s="14" t="inlineStr">
+        <is>
+          <t>ADC</t>
         </is>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>DF_robot</t>
-        </is>
-      </c>
-      <c r="B16" s="19" t="inlineStr">
-        <is>
-          <t>threshold</t>
-        </is>
-      </c>
-      <c r="C16" s="19" t="inlineStr">
-        <is>
-          <t>Front arrival reading</t>
-        </is>
-      </c>
-      <c r="E16" s="19" t="n">
+          <t>Watermark</t>
+        </is>
+      </c>
+      <c r="B16" s="28" t="inlineStr">
+        <is>
+          <t>air_val_max</t>
+        </is>
+      </c>
+      <c r="C16" s="28" t="inlineStr">
+        <is>
+          <t>Air value (max)</t>
+        </is>
+      </c>
+      <c r="D16" s="28" t="inlineStr">
+        <is>
+          <t>The maximum air value.</t>
+        </is>
+      </c>
+      <c r="E16" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="F16" s="19" t="n">
-        <v>1023</v>
-      </c>
-      <c r="G16" s="19" t="n">
-        <v>400</v>
+      <c r="F16" s="28" t="n">
+        <v>239</v>
+      </c>
+      <c r="G16" s="28" t="n">
+        <v>239</v>
       </c>
       <c r="H16" s="14" t="inlineStr">
         <is>
-          <t>ADC</t>
+          <t>kPa</t>
         </is>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>Watermark</t>
-        </is>
-      </c>
-      <c r="B17" s="19" t="inlineStr">
+          <t>Watermark_Temperature</t>
+        </is>
+      </c>
+      <c r="B17" s="28" t="inlineStr">
         <is>
           <t>air_val_max</t>
         </is>
       </c>
-      <c r="C17" s="19" t="inlineStr">
+      <c r="C17" s="28" t="inlineStr">
         <is>
           <t>Air value (max)</t>
         </is>
       </c>
-      <c r="E17" s="19" t="n">
+      <c r="D17" s="28" t="inlineStr">
+        <is>
+          <t>The maximum air value.</t>
+        </is>
+      </c>
+      <c r="E17" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="F17" s="19" t="n">
+      <c r="F17" s="28" t="n">
         <v>239</v>
       </c>
-      <c r="G17" s="19" t="n">
+      <c r="G17" s="28" t="n">
         <v>239</v>
       </c>
       <c r="H17" s="14" t="inlineStr">
@@ -3092,24 +3128,29 @@
           <t>Watermark_Temperature</t>
         </is>
       </c>
-      <c r="B18" s="19" t="inlineStr">
-        <is>
-          <t>air_val_max</t>
-        </is>
-      </c>
-      <c r="C18" s="19" t="inlineStr">
-        <is>
-          <t>Air value (max)</t>
-        </is>
-      </c>
-      <c r="E18" s="19" t="n">
+      <c r="B18" s="28" t="inlineStr">
+        <is>
+          <t>water_val</t>
+        </is>
+      </c>
+      <c r="C18" s="28" t="inlineStr">
+        <is>
+          <t>Water value</t>
+        </is>
+      </c>
+      <c r="D18" s="28" t="inlineStr">
+        <is>
+          <t>The set water value.</t>
+        </is>
+      </c>
+      <c r="E18" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="F18" s="19" t="n">
+      <c r="F18" s="28" t="n">
         <v>239</v>
       </c>
-      <c r="G18" s="19" t="n">
-        <v>239</v>
+      <c r="G18" s="28" t="n">
+        <v>0</v>
       </c>
       <c r="H18" s="14" t="inlineStr">
         <is>
@@ -3120,51 +3161,52 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>Watermark_Temperature</t>
-        </is>
-      </c>
-      <c r="B19" s="19" t="inlineStr">
-        <is>
-          <t>water_val</t>
-        </is>
-      </c>
-      <c r="C19" s="19" t="inlineStr">
-        <is>
-          <t>Water value</t>
-        </is>
-      </c>
-      <c r="E19" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="19" t="n">
-        <v>239</v>
-      </c>
-      <c r="G19" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="14" t="inlineStr">
-        <is>
-          <t>kPa</t>
+          <t>Watermark</t>
+        </is>
+      </c>
+      <c r="B19" s="28" t="inlineStr">
+        <is>
+          <t>soil_type</t>
+        </is>
+      </c>
+      <c r="C19" s="28" t="inlineStr">
+        <is>
+          <t>Soil Type</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr">
+        <is>
+          <t>Soil texture sets the irrigation thresholds. Choosing a type fills in the two tension values below, which you can still adjust.</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>Loam</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Loamy sand|Fine sandy loam|Sandy loam|Loam|Clay</t>
         </is>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>Watermark</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="inlineStr">
+          <t>Watermark_Temperature</t>
+        </is>
+      </c>
+      <c r="B20" s="28" t="inlineStr">
         <is>
           <t>soil_type</t>
         </is>
       </c>
-      <c r="C20" s="19" t="inlineStr">
+      <c r="C20" s="28" t="inlineStr">
         <is>
           <t>Soil Type</t>
         </is>
       </c>
-      <c r="D20" s="21" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>Soil texture sets the irrigation thresholds. Choosing a type fills in the two tension values below, which you can still adjust.</t>
         </is>
@@ -3183,32 +3225,36 @@
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>Watermark_Temperature</t>
-        </is>
-      </c>
-      <c r="B21" s="19" t="inlineStr">
-        <is>
-          <t>soil_type</t>
-        </is>
-      </c>
-      <c r="C21" s="19" t="inlineStr">
-        <is>
-          <t>Soil Type</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>Soil texture sets the irrigation thresholds. Choosing a type fills in the two tension values below, which you can still adjust.</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>Loam</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Loamy sand|Fine sandy loam|Sandy loam|Loam|Clay</t>
+          <t>Watermark</t>
+        </is>
+      </c>
+      <c r="B21" s="28" t="inlineStr">
+        <is>
+          <t>thr_low</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>Wet threshold (10% depletion)</t>
+        </is>
+      </c>
+      <c r="D21" s="29" t="inlineStr">
+        <is>
+          <t>Threshold to calculate how wet the soil is at 10% depletion.</t>
+        </is>
+      </c>
+      <c r="E21" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="29" t="n">
+        <v>239</v>
+      </c>
+      <c r="G21" s="29" t="n">
+        <v>23</v>
+      </c>
+      <c r="H21" s="14" t="inlineStr">
+        <is>
+          <t>kPa</t>
         </is>
       </c>
     </row>
@@ -3218,24 +3264,29 @@
           <t>Watermark</t>
         </is>
       </c>
-      <c r="B22" s="19" t="inlineStr">
-        <is>
-          <t>thr_low</t>
-        </is>
-      </c>
-      <c r="C22" s="21" t="inlineStr">
-        <is>
-          <t>Wet threshold (10% depletion)</t>
-        </is>
-      </c>
-      <c r="E22" s="16" t="n">
+      <c r="B22" s="28" t="inlineStr">
+        <is>
+          <t>thr_high</t>
+        </is>
+      </c>
+      <c r="C22" s="29" t="inlineStr">
+        <is>
+          <t>Dry threshold (40% depletion)</t>
+        </is>
+      </c>
+      <c r="D22" s="29" t="inlineStr">
+        <is>
+          <t>Threshold to calculate how dry the soil is at 40% depletion.</t>
+        </is>
+      </c>
+      <c r="E22" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="F22" s="16" t="n">
+      <c r="F22" s="29" t="n">
         <v>239</v>
       </c>
-      <c r="G22" s="16" t="n">
-        <v>23</v>
+      <c r="G22" s="29" t="n">
+        <v>65</v>
       </c>
       <c r="H22" s="14" t="inlineStr">
         <is>
@@ -3246,27 +3297,32 @@
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>Watermark</t>
-        </is>
-      </c>
-      <c r="B23" s="19" t="inlineStr">
-        <is>
-          <t>thr_high</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>Dry threshold (40% depletion)</t>
-        </is>
-      </c>
-      <c r="E23" s="16" t="n">
+          <t>Watermark_Temperature</t>
+        </is>
+      </c>
+      <c r="B23" s="28" t="inlineStr">
+        <is>
+          <t>thr_low</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Wet threshold (10% depletion)</t>
+        </is>
+      </c>
+      <c r="D23" s="29" t="inlineStr">
+        <is>
+          <t>Threshold to calculate how wet the soil is at 10% depletion.</t>
+        </is>
+      </c>
+      <c r="E23" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="F23" s="16" t="n">
+      <c r="F23" s="29" t="n">
         <v>239</v>
       </c>
-      <c r="G23" s="16" t="n">
-        <v>65</v>
+      <c r="G23" s="29" t="n">
+        <v>23</v>
       </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
@@ -3280,24 +3336,29 @@
           <t>Watermark_Temperature</t>
         </is>
       </c>
-      <c r="B24" s="19" t="inlineStr">
-        <is>
-          <t>thr_low</t>
+      <c r="B24" s="28" t="inlineStr">
+        <is>
+          <t>thr_high</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Wet threshold (10% depletion)</t>
-        </is>
-      </c>
-      <c r="E24" s="16" t="n">
+          <t>Dry threshold (40% depletion)</t>
+        </is>
+      </c>
+      <c r="D24" s="29" t="inlineStr">
+        <is>
+          <t>Threshold to calculate how dry the soil is at 40% depletion.</t>
+        </is>
+      </c>
+      <c r="E24" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="F24" s="16" t="n">
+      <c r="F24" s="29" t="n">
         <v>239</v>
       </c>
-      <c r="G24" s="16" t="n">
-        <v>23</v>
+      <c r="G24" s="29" t="n">
+        <v>65</v>
       </c>
       <c r="H24" s="14" t="inlineStr">
         <is>
@@ -3306,33 +3367,34 @@
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>Watermark_Temperature</t>
-        </is>
-      </c>
-      <c r="B25" s="19" t="inlineStr">
-        <is>
-          <t>thr_high</t>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Watermark</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>wiring</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dry threshold (40% depletion)</t>
-        </is>
-      </c>
-      <c r="E25" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="16" t="n">
-        <v>239</v>
-      </c>
-      <c r="G25" s="16" t="n">
-        <v>65</v>
-      </c>
-      <c r="H25" s="14" t="inlineStr">
-        <is>
-          <t>kPa</t>
+          <t>Connection</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>How the sensor reaches the board. Through the 200SS-VA3 adapter, which does the excitation and calibration itself, or wired straight to the Arduino with a series resistor. Direct wiring supports one Watermark only: two bare sensors in the same soil read through each other and damage their electrodes.</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>200SS-VA3 adapter</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>200SS-VA3 adapter|Direct to Arduino</t>
         </is>
       </c>
     </row>
@@ -3344,131 +3406,135 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>wiring</t>
+          <t>Rx</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Connection</t>
+          <t>Series resistor</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>How the sensor reaches the board. Through the 200SS-VA3 adapter, which does the excitation and calibration itself, or wired straight to the Arduino with a series resistor. Direct wiring supports one Watermark only: two bare sensors in the same soil read through each other and damage their electrodes.</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>200SS-VA3 adapter</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>200SS-VA3 adapter|Direct to Arduino</t>
+          <t>Series resistor between the sensor and ground, used only for direct wiring. Irrometer's reference circuit uses 10 kilohms.</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>100</v>
+      </c>
+      <c r="G26" t="n">
+        <v>10</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>kOhm</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Watermark</t>
+          <t>Temperature</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Rx</t>
+          <t>wiring</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Series resistor</t>
+          <t>Connection</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Series resistor between the sensor and ground, used only for direct wiring. Irrometer's reference circuit uses 10 kilohms.</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>1</v>
-      </c>
-      <c r="F27" t="n">
-        <v>100</v>
-      </c>
-      <c r="G27" t="n">
-        <v>10</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>kOhm</t>
+          <t>How the sensor reaches the board. Through the 200SS-VA3 adapter, which does the excitation and calibration itself, or wired straight to the Arduino with a series resistor. Direct wiring supports one Watermark only: two bare sensors in the same soil read through each other and damage their electrodes.</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>200SS-VA3 adapter</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>200SS-VA3 adapter|Direct to Arduino</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Watermark_Temperature</t>
+          <t>Temperature</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>wiring</t>
+          <t>Rx</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Connection</t>
+          <t>Series resistor</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>How the sensor reaches the board. Through the 200SS-VA3 adapter, which does the excitation and calibration itself, or wired straight to the Arduino with a series resistor. Direct wiring supports one Watermark only: two bare sensors in the same soil read through each other and damage their electrodes.</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>200SS-VA3 adapter</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>200SS-VA3 adapter|Direct to Arduino</t>
+          <t>Series resistor between the sensor and ground, used only for direct wiring. Irrometer's reference circuit uses 10 kilohms.</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" t="n">
+        <v>100</v>
+      </c>
+      <c r="G28" t="n">
+        <v>10</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>kOhm</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Watermark_Temperature</t>
+          <t>Watermark</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Rx</t>
+          <t>soil_temp_c</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Series resistor</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Series resistor between the sensor and ground, used only for direct wiring. Irrometer's reference circuit uses 10 kilohms.</t>
+          <t>Soil temperature</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Soil temperature used to compensate the Watermark calibration when wiring direct. Irrometer uses 24 C when no temperature sensor is available.</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>-10</v>
       </c>
       <c r="F29" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="G29" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>kOhm</t>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -3480,27 +3546,31 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>wiring</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Connection</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>How the sensor reaches the board. Through the 200SS-VA3 adapter, which does the excitation and calibration itself, or wired straight to the Arduino with a series resistor. Direct wiring supports one Watermark only: two bare sensors in the same soil read through each other and damage their electrodes.</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>200SS-VA3 adapter</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>200SS-VA3 adapter|Direct to Arduino</t>
+          <t>therm_r25</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Thermistor R at 25 C</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>Resistance of the 200TS at 25 C, for direct wiring. NOT PUBLISHED BY IRROMETER: the datasheet says the curve is built into their reading devices. The default assumes a generic 10 kilohm NTC and must be checked against your sensor before the reading is trusted.</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100</v>
+      </c>
+      <c r="F30" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G30" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Ohm</t>
         </is>
       </c>
     </row>
@@ -3512,142 +3582,37 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Rx</t>
+          <t>therm_beta</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Series resistor</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Series resistor between the sensor and ground, used only for direct wiring. Irrometer's reference circuit uses 10 kilohms.</t>
+          <t>Thermistor beta</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Beta coefficient of the 200TS, for direct wiring. Same caveat as the resistance above: this is a generic NTC value, not an Irrometer figure.</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="F31" t="n">
-        <v>100</v>
+        <v>6000</v>
       </c>
       <c r="G31" t="n">
-        <v>10</v>
+        <v>3435</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>kOhm</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Watermark</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>soil_temp_c</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Soil temperature</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Soil temperature used to compensate the Watermark calibration when wiring direct. Irrometer uses 24 C when no temperature sensor is available.</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>-10</v>
-      </c>
-      <c r="F32" t="n">
-        <v>60</v>
-      </c>
-      <c r="G32" t="n">
-        <v>24</v>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Temperature</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>therm_r25</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Thermistor R at 25 C</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Resistance of the 200TS at 25 C, for direct wiring. NOT PUBLISHED BY IRROMETER: the datasheet says the curve is built into their reading devices. The default assumes a generic 10 kilohm NTC and must be checked against your sensor before the reading is trusted.</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>100</v>
-      </c>
-      <c r="F33" t="n">
-        <v>100000</v>
-      </c>
-      <c r="G33" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Ohm</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Temperature</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>therm_beta</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Thermistor beta</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Beta coefficient of the 200TS, for direct wiring. Same caveat as the resistance above: this is a generic NTC value, not an Irrometer figure.</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F34" t="n">
-        <v>6000</v>
-      </c>
-      <c r="G34" t="n">
-        <v>3435</v>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
           <t>K</t>
         </is>
       </c>
     </row>
+    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
     <row r="35" ht="15.75" customHeight="1"/>
     <row r="36" ht="15.75" customHeight="1"/>
     <row r="37" ht="15.75" customHeight="1"/>
@@ -5907,9 +5872,9 @@
           <t>D1</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Digital pin 1. Shared with the USB serial line: using it breaks uploads and the serial monitor.</t>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Digital pin 1.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -5924,9 +5889,9 @@
           <t>D2</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Digital pin 2. Free on the shield, currently used as a direct-wiring excitation pin.</t>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Digital pin 2.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -5941,9 +5906,9 @@
           <t>D3</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Digital pin 3. Free on the shield, currently used as a direct-wiring excitation pin.</t>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Digital pin 3. </t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -5958,9 +5923,9 @@
           <t>D4</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Digital pin 4. Used by the LCD keypad shield.</t>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Digital pin 4.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -5975,9 +5940,9 @@
           <t>D5</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Digital pin 5. Used by the LCD keypad shield.</t>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Digital pin 5. </t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -5992,9 +5957,9 @@
           <t>D6</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Digital pin 6. Used by the LCD keypad shield.</t>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Digital pin 6. </t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -6009,9 +5974,9 @@
           <t>D7</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Digital pin 7. Used by the LCD keypad shield.</t>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Digital pin 7. </t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -6026,9 +5991,9 @@
           <t>D8</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Digital pin 8. Used by the LCD keypad shield.</t>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Digital pin 8. </t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -6043,9 +6008,9 @@
           <t>D9</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Digital pin 9. Used by the LCD keypad shield.</t>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Digital pin 9. </t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -6060,9 +6025,9 @@
           <t>D10</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Digital pin 10. Drives the LCD backlight.</t>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Digital pin 10.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -6077,9 +6042,9 @@
           <t>D11</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Digital pin 11. Free on the shield.</t>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Digital pin 11.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -6094,9 +6059,9 @@
           <t>D12</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Digital pin 12. Free on the shield.</t>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Digital pin 12. </t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -6111,9 +6076,9 @@
           <t>D13</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Digital pin 13. Free, but shares the onboard LED.</t>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Digital pin 13.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -7332,7 +7297,7 @@
           <t>Displays soil tension in kPa</t>
         </is>
       </c>
-      <c r="D10" s="16" t="b">
+      <c r="D10" s="29" t="b">
         <v>1</v>
       </c>
     </row>

--- a/data/sensor_configuration_v2.xlsx
+++ b/data/sensor_configuration_v2.xlsx
@@ -1,149 +1,936 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10511"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fernandolaguna/Desktop/Low-Cost-Water-Tech/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE5DCCCB-5358-2D4C-B25D-14E28B468320}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="1360" yWindow="5620" windowWidth="28800" windowHeight="17400" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="17400" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="sensors" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="params" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="survey_questions" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="ports" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="viz_options" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="sensors" sheetId="1" r:id="rId1"/>
+    <sheet name="params" sheetId="2" r:id="rId2"/>
+    <sheet name="survey_questions" sheetId="3" r:id="rId3"/>
+    <sheet name="ports" sheetId="4" r:id="rId4"/>
+    <sheet name="viz_options" sheetId="5" r:id="rId5"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="259">
+  <si>
+    <t>sensor_name</t>
+  </si>
+  <si>
+    <t>output_value</t>
+  </si>
+  <si>
+    <t>full_name</t>
+  </si>
+  <si>
+    <t>info_tip</t>
+  </si>
+  <si>
+    <t>in_a</t>
+  </si>
+  <si>
+    <t>in_b</t>
+  </si>
+  <si>
+    <t>in_c</t>
+  </si>
+  <si>
+    <t>in_d</t>
+  </si>
+  <si>
+    <t>in_e</t>
+  </si>
+  <si>
+    <t>equation</t>
+  </si>
+  <si>
+    <t>Units</t>
+  </si>
+  <si>
+    <t>viz</t>
+  </si>
+  <si>
+    <t>Soil moisture capacitive sensor (such as the DFRobot SEN0308)</t>
+  </si>
+  <si>
+    <t>Raw Value (ADC)</t>
+  </si>
+  <si>
+    <t>Raw Sensor Value (ADC)</t>
+  </si>
+  <si>
+    <t>Direct sensor reading (Analog to Digital conversion)</t>
+  </si>
+  <si>
+    <t>air_val_min</t>
+  </si>
+  <si>
+    <t>kΩ</t>
+  </si>
+  <si>
+    <t>raw_lcd</t>
+  </si>
+  <si>
+    <t>Raw Value (%)</t>
+  </si>
+  <si>
+    <t>Raw Sensor Value (%)</t>
+  </si>
+  <si>
+    <t>We will transform the raw value and express it as a percentage - 0% corresponds to the lowest possible value (dry) and 100% corresponds to the higest possible value (wet).</t>
+  </si>
+  <si>
+    <t>air_val_max</t>
+  </si>
+  <si>
+    <t>water_val</t>
+  </si>
+  <si>
+    <t>(X-min)/(max-min)*100</t>
+  </si>
+  <si>
+    <t>kPa</t>
+  </si>
+  <si>
+    <t>bar|transformed_lcd</t>
+  </si>
+  <si>
+    <t>Thresholds</t>
+  </si>
+  <si>
+    <t>Management Thresholds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This variable will tell you if the soil is very dry, dry or wet. It transforms the raw value into these three qualitative states, using two thresholds that you specify. </t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>b</t>
+  </si>
+  <si>
+    <t>x &gt; a → 'Too a' x &gt; b → 'v ab' → 'good'</t>
+  </si>
+  <si>
+    <t>state_lcd</t>
+  </si>
+  <si>
+    <t>Wetting Front</t>
+  </si>
+  <si>
+    <t>Wetting Front arrival at sensor's depth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This variables specifies when the water has arrived at the depth at which the sensor is positioned. </t>
+  </si>
+  <si>
+    <t>shallow</t>
+  </si>
+  <si>
+    <t>deep</t>
+  </si>
+  <si>
+    <t>threshold</t>
+  </si>
+  <si>
+    <t>wetting has arrived at XX cm</t>
+  </si>
+  <si>
+    <t>front_lcd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">there are 2 sensors at diff depths (shallow and deep - they have to specify those depths). They specify a threshold at which they consider water has arrived "suffuciently) and this is what says the wetting front has arrived at depth a/b. If value at depth a &lt; threshold, then "wetting front has arrived at depth a. Same for b. As long as b&gt;threshold, check a and put a in visualisation. If b&lt;threshold, then show b setting. </t>
+  </si>
+  <si>
+    <t>1-2-3 point calibrations</t>
+  </si>
+  <si>
+    <t>Quick 1, 2 or 3 point calibration procedure</t>
+  </si>
+  <si>
+    <t>TO ADD if relevant (not yet implemented)</t>
+  </si>
+  <si>
+    <t>soil_moisture-WP*100/(FC-WP)</t>
+  </si>
+  <si>
+    <t>Rate of Change of Soil Water Status</t>
+  </si>
+  <si>
+    <t>Rate of Change</t>
+  </si>
+  <si>
+    <t>dV/dt = a(good or stop irrigating)</t>
+  </si>
+  <si>
+    <t>check and to implement afterwards</t>
+  </si>
+  <si>
+    <t>Volumetric Soil Moisture</t>
+  </si>
+  <si>
+    <t>The volumetric soil moisture content, expressed here as a percentage (%), references to the volume of water reported to the volume of soil. It is calculated as θv = Vw/Vs⋅100 where Vw is  the water volume, Vs the dry soil volume.</t>
+  </si>
+  <si>
+    <t>air_val</t>
+  </si>
+  <si>
+    <t>FC</t>
+  </si>
+  <si>
+    <t>WP</t>
+  </si>
+  <si>
+    <t>1/k*ln(V-water_val)/(air_val-water_val)</t>
+  </si>
+  <si>
+    <t>bar|transformed_lcd|state_lcd</t>
+  </si>
+  <si>
+    <t>check paper Vandome et al. 2023?</t>
+  </si>
+  <si>
+    <t>Vertical Flow Rate</t>
+  </si>
+  <si>
+    <t>rate_lcd</t>
+  </si>
+  <si>
+    <t>Total Available Water</t>
+  </si>
+  <si>
+    <t>Available water capacity is the amount of water that can be stored in a soil profile and be available for growing crops. It is also known as available water content (AWC), profile available water (PAW) or total available water (TAW).</t>
+  </si>
+  <si>
+    <t>soil_moisture is calculated just aove</t>
+  </si>
+  <si>
+    <t>Irrometer Watermark (200SS)</t>
+  </si>
+  <si>
+    <t>Raw value (Resistance)</t>
+  </si>
+  <si>
+    <t>Raw value (Resistance, in kΩ)</t>
+  </si>
+  <si>
+    <t>Electrical resistance of the granular matrix, in kilohms. This is only available when the sensor is wired straight to the Arduino. Through the 200SS-VA3 adapter the resistance never leaves the adapter, so on that wiring the reading shown is tension in kPa instead.</t>
+  </si>
+  <si>
+    <t>Rx*(Vs-A1)/A1</t>
+  </si>
+  <si>
+    <t>This sensor measures electrical resistance inside a granular matrix to determine soil water tension. With this option, you are reading the resistance value (kΩ), expressed as a percentage - 0% corresponds to the lowest possible value and 100% corresponds to the higest possible value.</t>
+  </si>
+  <si>
+    <t>abs(air_val_max)</t>
+  </si>
+  <si>
+    <t>wm_state_lcd|bar|transformed_lcd</t>
+  </si>
+  <si>
+    <t>revise equation?</t>
+  </si>
+  <si>
+    <t>Tension (kPa)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This sensor measures electrical resistance inside a granular matrix to determine soil water tension. Once resistance is known, a calibration equation converts the value to soil water tension (kPa), using the following equation: kPa = (−3.213 × R − 4.093) / (1 − 0.009733 × R − 0,2892), where R is resistance in kΩ. This covers the range of 10 to 100 kPa. Values are linearly extrapolated for values below 10 kPa and above 100 kPa. You can use this option if you cannot measure soil temperature. </t>
+  </si>
+  <si>
+    <t>kpa_lcd</t>
+  </si>
+  <si>
+    <t>Tells you where the soil stands between (Dry plant stressed, Irrigation range, Saturation).</t>
+  </si>
+  <si>
+    <t>soil_type</t>
+  </si>
+  <si>
+    <t>thr_low</t>
+  </si>
+  <si>
+    <t>thr_high</t>
+  </si>
+  <si>
+    <t>wm_state_lcd</t>
+  </si>
+  <si>
+    <t>Irrometer Watermark (200SS) combined with Irrometer Soil Temperature Sensor (200TS)</t>
+  </si>
+  <si>
+    <t>Tension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This sensor measures electrical resistance inside a granular matrix to determine soil water tension. Once resistance is known, a calibration equation converts the value to soil water tension (kPa), using the following equation: kPa = (−3.213 × R − 4.093) / (1 − 0.009733 × R − 0.01205 × T), where R is resistance in kΩ and T is temperature in °C. This covers the range of 10 to 100 kPa. Values are linearly extrapolated for values below 10 kPa and above 100 kPa. Temperature affects the measured resistance; a temperature sensor input improves accuracy. . You can use this option if you can measure soil temperature. </t>
+  </si>
+  <si>
+    <t>Inside of the code itself for simplicity</t>
+  </si>
+  <si>
+    <t>Raw value (Temperature, in °F)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You are reading soil temperature in Fahrenheit using your soil temperature sensor. </t>
+  </si>
+  <si>
+    <t>20 + 48.48(V-0.49)</t>
+  </si>
+  <si>
+    <t>°F</t>
+  </si>
+  <si>
+    <t>temp_lcd</t>
+  </si>
+  <si>
+    <t>convert to °F + there is probably an equation on the Irrometer website that converts the analog reading to a temp</t>
+  </si>
+  <si>
+    <t>Raw value (Temperature, in °C)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You are reading soil temperature in Celsius using your soil temperature sensor. </t>
+  </si>
+  <si>
+    <t>((20+48.48(V-0.49)-32)/1.8)</t>
+  </si>
+  <si>
+    <t>°C</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> there is probably an equation on the Irrometer website that converts the analog reading to a temp</t>
+  </si>
+  <si>
+    <t>Irrometer Soil Temperature Sensor (200TS)</t>
+  </si>
+  <si>
+    <t>sensor_key</t>
+  </si>
+  <si>
+    <t>param_name</t>
+  </si>
+  <si>
+    <t>param_display_name</t>
+  </si>
+  <si>
+    <t>param_label (tooltip)</t>
+  </si>
+  <si>
+    <t>min</t>
+  </si>
+  <si>
+    <t>max</t>
+  </si>
+  <si>
+    <t>default_value</t>
+  </si>
+  <si>
+    <t>choices</t>
+  </si>
+  <si>
+    <t>DF_robot</t>
+  </si>
+  <si>
+    <t>Air value</t>
+  </si>
+  <si>
+    <t>Air value: raw reading in open air. The DFRobot probe outputs at most 2.9 V, about 593 counts on a 5 V board, so this sits just under 600.</t>
+  </si>
+  <si>
+    <t>ADC</t>
+  </si>
+  <si>
+    <t>Water value</t>
+  </si>
+  <si>
+    <t>Water value: the raw reading with the probe standing in water. Typically around 280 on a 5 V board. Measure it, do not assume it.</t>
+  </si>
+  <si>
+    <t>fc</t>
+  </si>
+  <si>
+    <t>Field Capacity</t>
+  </si>
+  <si>
+    <t>Field capacity: The amount of water that remains in the soil after all the excess water at saturation has been drained.</t>
+  </si>
+  <si>
+    <t>m³/m³</t>
+  </si>
+  <si>
+    <t>wp</t>
+  </si>
+  <si>
+    <t>Wilting point</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wilting point:  When plants take up all the available water for a given soil and it dries out to the point where it cannot supply any water to keep plants from dying </t>
+  </si>
+  <si>
+    <t>k</t>
+  </si>
+  <si>
+    <t>k: calibration scaling factor, fitted by matching gravimetric samples to the sensor. The default spreads a typical probe across 0 to about 50 % volumetric water, but it is soil specific and should be calibrated.</t>
+  </si>
+  <si>
+    <t>Watermark</t>
+  </si>
+  <si>
+    <t>Water value: raw reading submerged in water</t>
+  </si>
+  <si>
+    <t>Air value (minimum)</t>
+  </si>
+  <si>
+    <t>Air value: raw reading in open air</t>
+  </si>
+  <si>
+    <t>Air value (max)</t>
+  </si>
+  <si>
+    <t>Upper threshold</t>
+  </si>
+  <si>
+    <t>The upper threshold used to calculate the state of the sensor.</t>
+  </si>
+  <si>
+    <t>Lower threshold</t>
+  </si>
+  <si>
+    <t>The lower theshold used to calculate the state of the sensor.</t>
+  </si>
+  <si>
+    <t>Shallow sensor depth</t>
+  </si>
+  <si>
+    <t>The depth of the sensor closest to the surface.</t>
+  </si>
+  <si>
+    <t>cm</t>
+  </si>
+  <si>
+    <t>Deep sensor depth</t>
+  </si>
+  <si>
+    <t>The depth of the sensor deepest in the soil.</t>
+  </si>
+  <si>
+    <t>Front arrival reading</t>
+  </si>
+  <si>
+    <t>The threshold for the front arrival.</t>
+  </si>
+  <si>
+    <t>The maximum air value.</t>
+  </si>
+  <si>
+    <t>Watermark_Temperature</t>
+  </si>
+  <si>
+    <t>The set water value.</t>
+  </si>
+  <si>
+    <t>Soil Type</t>
+  </si>
+  <si>
+    <t>Soil texture sets the irrigation thresholds. Choosing a type fills in the two tension values below, which you can still adjust.</t>
+  </si>
+  <si>
+    <t>Loam</t>
+  </si>
+  <si>
+    <t>Loamy sand|Fine sandy loam|Sandy loam|Loam|Clay</t>
+  </si>
+  <si>
+    <t>Wet threshold (10% depletion)</t>
+  </si>
+  <si>
+    <t>Threshold to calculate how wet the soil is at 10% depletion.</t>
+  </si>
+  <si>
+    <t>Dry threshold (40% depletion)</t>
+  </si>
+  <si>
+    <t>Threshold to calculate how dry the soil is at 40% depletion.</t>
+  </si>
+  <si>
+    <t>wiring</t>
+  </si>
+  <si>
+    <t>Connection</t>
+  </si>
+  <si>
+    <t>How the sensor reaches the board. Through the 200SS-VA3 adapter, which does the excitation and calibration itself, or wired straight to the Arduino with a series resistor. Direct wiring supports one Watermark only: two bare sensors in the same soil read through each other and damage their electrodes.</t>
+  </si>
+  <si>
+    <t>200SS-VA3 adapter</t>
+  </si>
+  <si>
+    <t>200SS-VA3 adapter|Direct to Arduino</t>
+  </si>
+  <si>
+    <t>Rx</t>
+  </si>
+  <si>
+    <t>Series resistor</t>
+  </si>
+  <si>
+    <t>Series resistor between the sensor and ground, used only for direct wiring. Irrometer's reference circuit uses 10 kilohms.</t>
+  </si>
+  <si>
+    <t>kOhm</t>
+  </si>
+  <si>
+    <t>Temperature</t>
+  </si>
+  <si>
+    <t>soil_temp_c</t>
+  </si>
+  <si>
+    <t>Soil temperature</t>
+  </si>
+  <si>
+    <t>Soil temperature used to compensate the Watermark calibration when wiring direct. Irrometer uses 24 C when no temperature sensor is available.</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>therm_r25</t>
+  </si>
+  <si>
+    <t>Thermistor R at 25 C</t>
+  </si>
+  <si>
+    <t>Resistance of the 200TS at 25 C, for direct wiring. NOT PUBLISHED BY IRROMETER: the datasheet says the curve is built into their reading devices. The default assumes a generic 10 kilohm NTC and must be checked against your sensor before the reading is trusted.</t>
+  </si>
+  <si>
+    <t>Ohm</t>
+  </si>
+  <si>
+    <t>therm_beta</t>
+  </si>
+  <si>
+    <t>Thermistor beta</t>
+  </si>
+  <si>
+    <t>Beta coefficient of the 200TS, for direct wiring. Same caveat as the resistance above: this is a generic NTC value, not an Irrometer figure.</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>question_key</t>
+  </si>
+  <si>
+    <t>question_label</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>required (TRUE/FALSE)</t>
+  </si>
+  <si>
+    <t>options / placeholder</t>
+  </si>
+  <si>
+    <t>filename</t>
+  </si>
+  <si>
+    <t>File name</t>
+  </si>
+  <si>
+    <t>text</t>
+  </si>
+  <si>
+    <t>TRUE</t>
+  </si>
+  <si>
+    <t>e.g. apples_field2 (no spaces, no .ino)</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>Your name</t>
+  </si>
+  <si>
+    <t>e.g. John R.</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>Country</t>
+  </si>
+  <si>
+    <t>e.g. United States of America</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>Email address</t>
+  </si>
+  <si>
+    <t>e.g. name@example.com</t>
+  </si>
+  <si>
+    <t>ino_comment</t>
+  </si>
+  <si>
+    <t>Comment to include in the code (optional)</t>
+  </si>
+  <si>
+    <t>FALSE</t>
+  </si>
+  <si>
+    <t>e.g. Orchard block 2, installed June 2026</t>
+  </si>
+  <si>
+    <t>port_value</t>
+  </si>
+  <si>
+    <t>port_tip</t>
+  </si>
+  <si>
+    <t>active (TRUE/FALSE)</t>
+  </si>
+  <si>
+    <t>A1</t>
+  </si>
+  <si>
+    <t>Analog pin A1. A0 is taken by the shield's buttons, so sensors start here.</t>
+  </si>
+  <si>
+    <t>A2</t>
+  </si>
+  <si>
+    <t>Analog pin A2.</t>
+  </si>
+  <si>
+    <t>A3</t>
+  </si>
+  <si>
+    <t>Analog pin A3.</t>
+  </si>
+  <si>
+    <t>A4</t>
+  </si>
+  <si>
+    <t>Analog pin A4.</t>
+  </si>
+  <si>
+    <t>A5</t>
+  </si>
+  <si>
+    <t>Analog pin A5.</t>
+  </si>
+  <si>
+    <t>D1</t>
+  </si>
+  <si>
+    <t>Digital pin 1.</t>
+  </si>
+  <si>
+    <t>D2</t>
+  </si>
+  <si>
+    <t>Digital pin 2.</t>
+  </si>
+  <si>
+    <t>D3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Digital pin 3. </t>
+  </si>
+  <si>
+    <t>D4</t>
+  </si>
+  <si>
+    <t>Digital pin 4.</t>
+  </si>
+  <si>
+    <t>D5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Digital pin 5. </t>
+  </si>
+  <si>
+    <t>D6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Digital pin 6. </t>
+  </si>
+  <si>
+    <t>D7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Digital pin 7. </t>
+  </si>
+  <si>
+    <t>D8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Digital pin 8. </t>
+  </si>
+  <si>
+    <t>D9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Digital pin 9. </t>
+  </si>
+  <si>
+    <t>D10</t>
+  </si>
+  <si>
+    <t>Digital pin 10.</t>
+  </si>
+  <si>
+    <t>D11</t>
+  </si>
+  <si>
+    <t>Digital pin 11.</t>
+  </si>
+  <si>
+    <t>D12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Digital pin 12. </t>
+  </si>
+  <si>
+    <t>D13</t>
+  </si>
+  <si>
+    <t>Digital pin 13.</t>
+  </si>
+  <si>
+    <t>viz_key</t>
+  </si>
+  <si>
+    <t>label</t>
+  </si>
+  <si>
+    <t>viz_tip</t>
+  </si>
+  <si>
+    <t>none</t>
+  </si>
+  <si>
+    <t>No visualization</t>
+  </si>
+  <si>
+    <t>Display the information in a visual representation on the LCD screen. Currently there is nothing selected.</t>
+  </si>
+  <si>
+    <t>bar</t>
+  </si>
+  <si>
+    <t>Loading bar</t>
+  </si>
+  <si>
+    <t>Displays a loading bar that changes based on water content.</t>
+  </si>
+  <si>
+    <t>Raw value</t>
+  </si>
+  <si>
+    <t>Displays the raw sensor value</t>
+  </si>
+  <si>
+    <t>State: Very Dry, Dry, or Wet</t>
+  </si>
+  <si>
+    <t>Displays the general state at which soil seems to be for the capacitive sensors</t>
+  </si>
+  <si>
+    <t>transformed_lcd</t>
+  </si>
+  <si>
+    <t>Transformed Raw Value 0-100</t>
+  </si>
+  <si>
+    <t>A more concise version of the raw sensor value</t>
+  </si>
+  <si>
+    <t>rate</t>
+  </si>
+  <si>
+    <t>Rate of change (future)</t>
+  </si>
+  <si>
+    <t>The change in available water over time</t>
+  </si>
+  <si>
+    <t>Front detected</t>
+  </si>
+  <si>
+    <t>Shows front detected when the wetting front reaches the deep sensor</t>
+  </si>
+  <si>
+    <t>Displays the temperatue in celsius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRUE </t>
+  </si>
+  <si>
+    <t>Displays soil tension in kPa</t>
+  </si>
+  <si>
+    <t>Flow rate</t>
+  </si>
+  <si>
+    <t>Displays the flow rate between 2 sensors</t>
+  </si>
+  <si>
+    <t>State: Dry plant stressed, Irrigation range, or Saturation</t>
+  </si>
+  <si>
+    <t>Displays the state at which the soils seems to be for the Watermark sensors</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="19">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="10"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="10"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <family val="2"/>
-      <color rgb="FFFF0000"/>
-      <sz val="10"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color rgb="FFFF0000"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color rgb="FFFF0000"/>
-      <sz val="11"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="9"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="9"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="0"/>
       <name val="Arial"/>
       <family val="2"/>
-      <color theme="0"/>
-      <sz val="10"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="2"/>
       <name val="Arial"/>
       <family val="2"/>
-      <color theme="2"/>
-      <sz val="10"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FFFFFF00"/>
       <name val="Arial"/>
       <family val="2"/>
-      <color rgb="FFFFFF00"/>
-      <sz val="10"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="-webkit-standard"/>
-      <color theme="1"/>
-      <sz val="11"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="3"/>
       <name val="Arial"/>
       <family val="2"/>
-      <color theme="3"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -218,146 +1005,81 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="28">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -558,1003 +1280,671 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:O34"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:O1001"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="35.33203125" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="40.83203125" customWidth="1" min="3" max="3"/>
-    <col width="39.5" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="6"/>
-    <col width="12" customWidth="1" min="7" max="9"/>
-    <col width="50" customWidth="1" min="10" max="10"/>
-    <col width="8.83203125" customWidth="1" min="11" max="26"/>
+    <col min="1" max="1" width="35.33203125" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="40.83203125" customWidth="1"/>
+    <col min="4" max="4" width="39.5" customWidth="1"/>
+    <col min="5" max="6" width="28" customWidth="1"/>
+    <col min="7" max="9" width="12" customWidth="1"/>
+    <col min="10" max="10" width="50" customWidth="1"/>
+    <col min="11" max="26" width="8.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>sensor_name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>output_value</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>full_name</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>info_tip</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>in_a</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>in_b</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>in_c</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>in_d</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>in_e</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>equation</t>
-        </is>
-      </c>
-      <c r="K1" s="2" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
-      <c r="L1" s="2" t="inlineStr">
-        <is>
-          <t>viz</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Soil moisture capacitive sensor (such as the DFRobot SEN0308)</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Raw Value (ADC)</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>Raw Sensor Value (ADC)</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>Direct sensor reading (Analog to Digital conversion)</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>air_val_min</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="3" t="n"/>
-      <c r="H2" s="3" t="n"/>
-      <c r="I2" s="3" t="n"/>
-      <c r="J2" s="3" t="n"/>
-      <c r="K2" s="4" t="inlineStr">
-        <is>
-          <t>kΩ</t>
-        </is>
-      </c>
-      <c r="L2" s="5" t="inlineStr">
-        <is>
-          <t>raw_lcd</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="n"/>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Raw Value (%)</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Raw Sensor Value (%)</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>We will transform the raw value and express it as a percentage - 0% corresponds to the lowest possible value (dry) and 100% corresponds to the higest possible value (wet).</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>air_val_max</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>water_val</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="n"/>
-      <c r="H3" s="3" t="n"/>
-      <c r="I3" s="3" t="n"/>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>(X-min)/(max-min)*100</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>kPa</t>
-        </is>
-      </c>
-      <c r="L3" s="5" t="inlineStr">
-        <is>
-          <t>bar|transformed_lcd</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="n"/>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Thresholds</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Management Thresholds</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">This variable will tell you if the soil is very dry, dry or wet. It transforms the raw value into these three qualitative states, using two thresholds that you specify. </t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="n"/>
-      <c r="H4" s="3" t="n"/>
-      <c r="I4" s="3" t="n"/>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>x &gt; a → 'Too a' x &gt; b → 'v ab' → 'good'</t>
-        </is>
-      </c>
-      <c r="K4" s="5" t="n"/>
-      <c r="L4" s="5" t="inlineStr">
-        <is>
-          <t>state_lcd</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Wetting Front</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Wetting Front arrival at sensor's depth</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">This variables specifies when the water has arrived at the depth at which the sensor is positioned. </t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>shallow</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>deep</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>threshold</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="n"/>
-      <c r="I5" s="3" t="n"/>
-      <c r="J5" s="6" t="n"/>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
-          <t>wetting has arrived at XX cm</t>
-        </is>
-      </c>
-      <c r="L5" s="5" t="inlineStr">
-        <is>
-          <t>front_lcd</t>
-        </is>
-      </c>
-      <c r="O5" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">there are 2 sensors at diff depths (shallow and deep - they have to specify those depths). They specify a threshold at which they consider water has arrived "suffuciently) and this is what says the wetting front has arrived at depth a/b. If value at depth a &lt; threshold, then "wetting front has arrived at depth a. Same for b. As long as b&gt;threshold, check a and put a in visualisation. If b&lt;threshold, then show b setting. </t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="18" t="n"/>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>1-2-3 point calibrations</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Quick 1, 2 or 3 point calibration procedure</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>TO ADD if relevant (not yet implemented)</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="n"/>
-      <c r="H6" s="3" t="n"/>
-      <c r="I6" s="3" t="n"/>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>soil_moisture-WP*100/(FC-WP)</t>
-        </is>
-      </c>
-      <c r="L6" s="5" t="inlineStr">
-        <is>
-          <t>bar|transformed_lcd</t>
-        </is>
-      </c>
-      <c r="O6" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">there are 2 sensors at diff depths (shallow and deep - they have to specify those depths). They specify a threshold at which they consider water has arrived "suffuciently) and this is what says the wetting front has arrived at depth a/b. If value at depth a &lt; threshold, then "wetting front has arrived at depth a. Same for b. As long as b&gt;threshold, check a and put a in visualisation. If b&lt;threshold, then show b setting. </t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="23" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Rate of Change of Soil Water Status</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Rate of Change</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>TO ADD if relevant (not yet implemented)</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="n"/>
-      <c r="F7" s="3" t="n"/>
-      <c r="G7" s="3" t="n"/>
-      <c r="H7" s="3" t="n"/>
-      <c r="I7" s="3" t="n"/>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>dV/dt = a(good or stop irrigating)</t>
-        </is>
-      </c>
-      <c r="K7" s="4" t="n"/>
-      <c r="L7" s="5" t="inlineStr">
-        <is>
-          <t>state_lcd</t>
-        </is>
-      </c>
-      <c r="O7" s="7" t="inlineStr">
-        <is>
-          <t>check and to implement afterwards</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="24" t="n"/>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Volumetric Soil Moisture</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Volumetric Soil Moisture</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>The volumetric soil moisture content, expressed here as a percentage (%), references to the volume of water reported to the volume of soil. It is calculated as θv = Vw/Vs⋅100 where Vw is  the water volume, Vs the dry soil volume.</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>air_val</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>water_val</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>FC</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>WP</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="n"/>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>1/k*ln(V-water_val)/(air_val-water_val)</t>
-        </is>
-      </c>
-      <c r="K8" s="8" t="n"/>
-      <c r="L8" s="8" t="inlineStr">
-        <is>
-          <t>bar|transformed_lcd|state_lcd</t>
-        </is>
-      </c>
-      <c r="O8" s="7" t="inlineStr">
-        <is>
-          <t>check paper Vandome et al. 2023?</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="24" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Vertical Flow Rate</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="n"/>
-      <c r="D9" s="3" t="n"/>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>shallow</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>deep</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>threshold</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="n"/>
-      <c r="I9" s="3" t="n"/>
-      <c r="J9" s="3" t="n"/>
-      <c r="K9" s="8" t="n"/>
-      <c r="L9" s="8" t="inlineStr">
-        <is>
-          <t>rate_lcd</t>
-        </is>
-      </c>
-      <c r="O9" s="7" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="24" t="n"/>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Total Available Water</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Total Available Water</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>Available water capacity is the amount of water that can be stored in a soil profile and be available for growing crops. It is also known as available water content (AWC), profile available water (PAW) or total available water (TAW).</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>air_val</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>water_val</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>FC</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>WP</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="n"/>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>soil_moisture-WP*100/(FC-WP)</t>
-        </is>
-      </c>
-      <c r="K10" s="8" t="n"/>
-      <c r="L10" s="8" t="inlineStr">
-        <is>
-          <t>bar|transformed_lcd|state_lcd</t>
-        </is>
-      </c>
-      <c r="O10" s="7" t="inlineStr">
-        <is>
-          <t>soil_moisture is calculated just aove</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Irrometer Watermark (200SS)</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Raw value (Resistance)</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Raw value (Resistance, in kΩ)</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Electrical resistance of the granular matrix, in kilohms. This is only available when the sensor is wired straight to the Arduino. Through the 200SS-VA3 adapter the resistance never leaves the adapter, so on that wiring the reading shown is tension in kPa instead.</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="n"/>
-      <c r="F11" s="3" t="n"/>
-      <c r="G11" s="3" t="n"/>
-      <c r="H11" s="3" t="n"/>
-      <c r="I11" s="3" t="n"/>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>Rx*(Vs-A1)/A1</t>
-        </is>
-      </c>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
-          <t>kΩ</t>
-        </is>
-      </c>
-      <c r="L11" s="5" t="inlineStr">
-        <is>
-          <t>raw_lcd</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="n"/>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Raw Value (%)</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Raw Sensor Value (%)</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>This sensor measures electrical resistance inside a granular matrix to determine soil water tension. With this option, you are reading the resistance value (kΩ), expressed as a percentage - 0% corresponds to the lowest possible value and 100% corresponds to the higest possible value.</t>
-        </is>
-      </c>
-      <c r="E12" s="26" t="inlineStr">
-        <is>
-          <t>abs(air_val_max)</t>
-        </is>
-      </c>
-      <c r="F12" s="26" t="inlineStr">
-        <is>
-          <t>water_val</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="n"/>
-      <c r="H12" s="6" t="n"/>
-      <c r="I12" s="6" t="n"/>
-      <c r="J12" s="26" t="inlineStr">
-        <is>
-          <t>(X-min)/(max-min)*100</t>
-        </is>
-      </c>
-      <c r="K12" s="5" t="inlineStr">
-        <is>
-          <t>kPa</t>
-        </is>
-      </c>
-      <c r="L12" s="5" t="inlineStr">
-        <is>
-          <t>wm_state_lcd|bar|transformed_lcd</t>
-        </is>
-      </c>
-      <c r="O12" s="9" t="inlineStr">
-        <is>
-          <t>revise equation?</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>Tension (kPa)</t>
-        </is>
-      </c>
-      <c r="C13" s="27" t="inlineStr">
-        <is>
-          <t>Tension (kPa)</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">This sensor measures electrical resistance inside a granular matrix to determine soil water tension. Once resistance is known, a calibration equation converts the value to soil water tension (kPa), using the following equation: kPa = (−3.213 × R − 4.093) / (1 − 0.009733 × R − 0,2892), where R is resistance in kΩ. This covers the range of 10 to 100 kPa. Values are linearly extrapolated for values below 10 kPa and above 100 kPa. You can use this option if you cannot measure soil temperature. </t>
-        </is>
-      </c>
-      <c r="L13" s="5" t="inlineStr">
-        <is>
-          <t>kpa_lcd</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>Management Thresholds</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>Management Thresholds</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>Tells you where the soil stands between (Dry plant stressed, Irrigation range, Saturation).</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>soil_type</t>
-        </is>
-      </c>
-      <c r="F14" s="29" t="inlineStr">
-        <is>
-          <t>thr_low</t>
-        </is>
-      </c>
-      <c r="G14" s="29" t="inlineStr">
-        <is>
-          <t>thr_high</t>
-        </is>
-      </c>
-      <c r="L14" s="5" t="inlineStr">
-        <is>
-          <t>wm_state_lcd</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Irrometer Watermark (200SS) combined with Irrometer Soil Temperature Sensor (200TS)</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Raw value (Resistance)</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Raw value (Resistance, in kΩ)</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>Electrical resistance of the granular matrix, in kilohms. This is only available when the sensor is wired straight to the Arduino. Through the 200SS-VA3 adapter the resistance never leaves the adapter, so on that wiring the reading shown is tension in kPa instead.</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="n"/>
-      <c r="F15" s="3" t="n"/>
-      <c r="G15" s="3" t="n"/>
-      <c r="H15" s="3" t="n"/>
-      <c r="I15" s="3" t="n"/>
-      <c r="J15" s="11" t="inlineStr">
-        <is>
-          <t>Rx*(Vs-A1)/A1</t>
-        </is>
-      </c>
-      <c r="K15" s="5" t="inlineStr">
-        <is>
-          <t>kPa</t>
-        </is>
-      </c>
-      <c r="L15" s="5" t="inlineStr">
-        <is>
-          <t>raw_lcd</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="n"/>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Raw Value (%)</t>
-        </is>
-      </c>
-      <c r="C16" s="26" t="inlineStr">
-        <is>
-          <t>Raw Sensor Value (%)</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>This sensor measures electrical resistance inside a granular matrix to determine soil water tension. With this option, you are reading the resistance value (kΩ), expressed as a percentage - 0% corresponds to the lowest possible value and 100% corresponds to the higest possible value.</t>
-        </is>
-      </c>
-      <c r="E16" s="26" t="inlineStr">
-        <is>
-          <t>abs(air_val_max)</t>
-        </is>
-      </c>
-      <c r="F16" s="26" t="inlineStr">
-        <is>
-          <t>water_val</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="n"/>
-      <c r="H16" s="6" t="n"/>
-      <c r="I16" s="6" t="n"/>
-      <c r="J16" s="26" t="inlineStr">
-        <is>
-          <t>(X-min)/(max-min)*100</t>
-        </is>
-      </c>
-      <c r="K16" s="5" t="inlineStr">
-        <is>
-          <t>kPa</t>
-        </is>
-      </c>
-      <c r="L16" s="5" t="inlineStr">
-        <is>
-          <t>wm_state_lcd|bar|transformed_lcd</t>
-        </is>
-      </c>
-      <c r="O16" s="9" t="inlineStr">
-        <is>
-          <t>revise equation?</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="n"/>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Tension</t>
-        </is>
-      </c>
-      <c r="C17" s="26" t="inlineStr">
-        <is>
-          <t>Tension</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">This sensor measures electrical resistance inside a granular matrix to determine soil water tension. Once resistance is known, a calibration equation converts the value to soil water tension (kPa), using the following equation: kPa = (−3.213 × R − 4.093) / (1 − 0.009733 × R − 0.01205 × T), where R is resistance in kΩ and T is temperature in °C. This covers the range of 10 to 100 kPa. Values are linearly extrapolated for values below 10 kPa and above 100 kPa. Temperature affects the measured resistance; a temperature sensor input improves accuracy. . You can use this option if you can measure soil temperature. </t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="n"/>
-      <c r="F17" s="3" t="n"/>
-      <c r="G17" s="3" t="n"/>
-      <c r="H17" s="3" t="n"/>
-      <c r="I17" s="3" t="n"/>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>Inside of the code itself for simplicity</t>
-        </is>
-      </c>
-      <c r="K17" s="5" t="inlineStr">
-        <is>
-          <t>kPa</t>
-        </is>
-      </c>
-      <c r="L17" s="5" t="inlineStr">
-        <is>
-          <t>kpa_lcd</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="n"/>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Raw value (Temperature, in °F)</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>Raw value (Temperature, in °F)</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">You are reading soil temperature in Fahrenheit using your soil temperature sensor. </t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="n"/>
-      <c r="F18" s="25" t="n"/>
-      <c r="G18" s="3" t="n"/>
-      <c r="H18" s="3" t="n"/>
-      <c r="I18" s="26" t="n"/>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>20 + 48.48(V-0.49)</t>
-        </is>
-      </c>
-      <c r="K18" s="5" t="inlineStr">
-        <is>
-          <t>°F</t>
-        </is>
-      </c>
-      <c r="L18" s="5" t="inlineStr">
-        <is>
-          <t>temp_lcd</t>
-        </is>
-      </c>
-      <c r="O18" s="9" t="inlineStr">
-        <is>
-          <t>convert to °F + there is probably an equation on the Irrometer website that converts the analog reading to a temp</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="n"/>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Raw value (Temperature, in °C)</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Raw value (Temperature, in °C)</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">You are reading soil temperature in Celsius using your soil temperature sensor. </t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="n"/>
-      <c r="F19" s="3" t="n"/>
-      <c r="G19" s="3" t="n"/>
-      <c r="H19" s="3" t="n"/>
-      <c r="I19" s="3" t="n"/>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>((20+48.48(V-0.49)-32)/1.8)</t>
-        </is>
-      </c>
-      <c r="K19" s="5" t="inlineStr">
-        <is>
-          <t>°C</t>
-        </is>
-      </c>
-      <c r="L19" s="5" t="inlineStr">
-        <is>
-          <t>temp_lcd</t>
-        </is>
-      </c>
-      <c r="O19" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> there is probably an equation on the Irrometer website that converts the analog reading to a temp</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="12" t="n"/>
-      <c r="B20" s="13" t="inlineStr">
-        <is>
-          <t>Management Thresholds</t>
-        </is>
-      </c>
-      <c r="C20" s="13" t="inlineStr">
-        <is>
-          <t>Management Thresholds</t>
-        </is>
-      </c>
-      <c r="D20" s="12" t="n"/>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>soil_type</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>thr_low</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>thr_high</t>
-        </is>
-      </c>
-      <c r="L20" s="5" t="inlineStr">
-        <is>
-          <t>wm_state_lcd</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="22" t="inlineStr">
-        <is>
-          <t>Irrometer Soil Temperature Sensor (200TS)</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Raw value (Temperature, in °F)</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>Raw value (Temperature, in °F)</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">You are reading soil temperature in Fahrenheit using your soil temperature sensor. </t>
-        </is>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>20 + 48.48(V-0.49)</t>
-        </is>
-      </c>
-      <c r="K21" s="5" t="inlineStr">
-        <is>
-          <t>°F</t>
-        </is>
-      </c>
-      <c r="L21" s="5" t="inlineStr">
-        <is>
-          <t>temp_lcd</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="12" t="n"/>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Raw value (Temperature, in °C)</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>Raw value (Temperature, in °C)</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">You are reading soil temperature in Celsius using your soil temperature sensor. </t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>((20+48.48(V-0.49)-32)/1.8)</t>
-        </is>
-      </c>
-      <c r="K22" s="5" t="inlineStr">
-        <is>
-          <t>°C</t>
-        </is>
-      </c>
-      <c r="L22" s="5" t="inlineStr">
-        <is>
-          <t>temp_lcd</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="12" t="n"/>
-      <c r="B23" s="12" t="n"/>
-      <c r="C23" s="12" t="n"/>
-      <c r="D23" s="12" t="n"/>
-    </row>
-    <row r="24" ht="15.75" customHeight="1"/>
-    <row r="25" ht="15.75" customHeight="1"/>
-    <row r="26" ht="15.75" customHeight="1"/>
-    <row r="27" ht="15.75" customHeight="1"/>
-    <row r="28" ht="15.75" customHeight="1"/>
-    <row r="29" ht="15.75" customHeight="1"/>
-    <row r="30" ht="15.75" customHeight="1"/>
-    <row r="31" ht="15.75" customHeight="1"/>
-    <row r="32" ht="15.75" customHeight="1"/>
-    <row r="33" ht="15.75" customHeight="1"/>
-    <row r="34" ht="15.75" customHeight="1">
-      <c r="D34" s="5" t="n"/>
-    </row>
-    <row r="35" ht="15.75" customHeight="1"/>
-    <row r="36" ht="15.75" customHeight="1"/>
-    <row r="37" ht="15.75" customHeight="1"/>
-    <row r="38" ht="15.75" customHeight="1"/>
-    <row r="39" ht="15.75" customHeight="1"/>
-    <row r="40" ht="15.75" customHeight="1"/>
-    <row r="41" ht="15.75" customHeight="1"/>
-    <row r="42" ht="15.75" customHeight="1"/>
-    <row r="43" ht="15.75" customHeight="1"/>
-    <row r="44" ht="15.75" customHeight="1"/>
-    <row r="45" ht="15.75" customHeight="1"/>
-    <row r="46" ht="15.75" customHeight="1"/>
-    <row r="47" ht="15.75" customHeight="1"/>
-    <row r="48" ht="15.75" customHeight="1"/>
+    <row r="1" spans="1:15">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
+      <c r="A2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="O5" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" s="18"/>
+      <c r="B6" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="O6" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" s="23"/>
+      <c r="B7" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K7" s="4"/>
+      <c r="L7" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="O7" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" s="24"/>
+      <c r="B8" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="O8" s="7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" s="24"/>
+      <c r="B9" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="8"/>
+      <c r="L9" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="O9" s="7"/>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" s="24"/>
+      <c r="B10" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="O10" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L11" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E12" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="F12" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L12" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="O12" s="9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="B13" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" s="27" t="s">
+        <v>73</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="L13" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="15" customHeight="1">
+      <c r="B14" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="G14" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="L14" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="A15" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L15" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E16" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="F16" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L16" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="O16" s="9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C17" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L17" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E18" s="3"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="26"/>
+      <c r="J18" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="L18" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="O18" s="9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="L19" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="O19" s="7" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15">
+      <c r="A20" s="12"/>
+      <c r="B20" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" s="12"/>
+      <c r="E20" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="L20" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15">
+      <c r="A21" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="L21" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A22" s="12"/>
+      <c r="B22" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="K22" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="L22" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A23" s="12"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+    </row>
+    <row r="24" spans="1:15" ht="15.75" customHeight="1"/>
+    <row r="25" spans="1:15" ht="15.75" customHeight="1"/>
+    <row r="26" spans="1:15" ht="15.75" customHeight="1"/>
+    <row r="27" spans="1:15" ht="15.75" customHeight="1"/>
+    <row r="28" spans="1:15" ht="15.75" customHeight="1"/>
+    <row r="29" spans="1:15" ht="15.75" customHeight="1"/>
+    <row r="30" spans="1:15" ht="15.75" customHeight="1"/>
+    <row r="31" spans="1:15" ht="15.75" customHeight="1"/>
+    <row r="32" spans="1:15" ht="15.75" customHeight="1"/>
+    <row r="33" spans="4:4" ht="15.75" customHeight="1"/>
+    <row r="34" spans="4:4" ht="15.75" customHeight="1">
+      <c r="D34" s="5"/>
+    </row>
+    <row r="35" spans="4:4" ht="15.75" customHeight="1"/>
+    <row r="36" spans="4:4" ht="15.75" customHeight="1"/>
+    <row r="37" spans="4:4" ht="15.75" customHeight="1"/>
+    <row r="38" spans="4:4" ht="15.75" customHeight="1"/>
+    <row r="39" spans="4:4" ht="15.75" customHeight="1"/>
+    <row r="40" spans="4:4" ht="15.75" customHeight="1"/>
+    <row r="41" spans="4:4" ht="15.75" customHeight="1"/>
+    <row r="42" spans="4:4" ht="15.75" customHeight="1"/>
+    <row r="43" spans="4:4" ht="15.75" customHeight="1"/>
+    <row r="44" spans="4:4" ht="15.75" customHeight="1"/>
+    <row r="45" spans="4:4" ht="15.75" customHeight="1"/>
+    <row r="46" spans="4:4" ht="15.75" customHeight="1"/>
+    <row r="47" spans="4:4" ht="15.75" customHeight="1"/>
+    <row r="48" spans="4:4" ht="15.75" customHeight="1"/>
     <row r="49" ht="15.75" customHeight="1"/>
     <row r="50" ht="15.75" customHeight="1"/>
     <row r="51" ht="15.75" customHeight="1"/>
@@ -2515,1102 +2905,784 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I31"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:I1000"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="3"/>
-    <col width="48" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="8.83203125" customWidth="1" min="8" max="26"/>
+    <col min="1" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="48" customWidth="1"/>
+    <col min="5" max="6" width="8" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="26" width="8.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>sensor_key</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>param_name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>param_display_name</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>param_label (tooltip)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>min</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>max</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>default_value</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>DF_robot</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>air_val</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>Air value</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>Air value: raw reading in open air. The DFRobot probe outputs at most 2.9 V, about 593 counts on a 5 V board, so this sits just under 600.</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="n">
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="E2" s="3">
         <v>0</v>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="F2" s="3">
         <v>1023</v>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="G2" s="3">
         <v>590</v>
       </c>
-      <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>ADC</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>DF_robot</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>water_val</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Water value</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Water value: the raw reading with the probe standing in water. Typically around 280 on a 5 V board. Measure it, do not assume it.</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="n">
+      <c r="H2" s="5" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="E3" s="3">
         <v>0</v>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="F3" s="3">
         <v>1023</v>
       </c>
-      <c r="G3" s="3" t="n">
-        <v>280</v>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>ADC</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>DF_robot</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>fc</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Field Capacity</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Field capacity: The amount of water that remains in the soil after all the excess water at saturation has been drained.</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="n">
+      <c r="G3" s="3">
         <v>0</v>
       </c>
-      <c r="F4" s="3" t="n">
+      <c r="H3" s="5" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
         <v>1</v>
       </c>
-      <c r="G4" s="3" t="n">
+      <c r="G4" s="3">
         <v>0.3</v>
       </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>m³/m³</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>DF_robot</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>wp</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Wilting point</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Wilting point:  When plants take up all the available water for a given soil and it dries out to the point where it cannot supply any water to keep plants from dying </t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="n">
+      <c r="H4" s="5" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E5" s="3">
         <v>0</v>
       </c>
-      <c r="F5" s="3" t="n">
+      <c r="F5" s="3">
         <v>1</v>
       </c>
-      <c r="G5" s="3" t="n">
+      <c r="G5" s="3">
         <v>0.1</v>
       </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>m³/m³</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>DF_robot</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>k</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>k</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>k: calibration scaling factor, fitted by matching gravimetric samples to the sensor. The default spreads a typical probe across 0 to about 50 % volumetric water, but it is soil specific and should be calibrated.</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="n">
+      <c r="H5" s="5" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="E6" s="3">
         <v>0</v>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="F6" s="3">
         <v>10</v>
       </c>
-      <c r="G6" s="3" t="n">
+      <c r="G6" s="3">
         <v>6.1</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="10" t="n"/>
-      <c r="B7" s="10" t="n"/>
-      <c r="C7" s="10" t="n"/>
-      <c r="D7" s="10" t="n"/>
-      <c r="E7" s="10" t="n"/>
-      <c r="F7" s="10" t="n"/>
-      <c r="G7" s="10" t="n"/>
-      <c r="H7" s="5" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>Watermark</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>water_val</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>Water value</t>
-        </is>
-      </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>Water value: raw reading submerged in water</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="n">
+    <row r="7" spans="1:9">
+      <c r="A7" s="10"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="5"/>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="E8" s="10">
         <v>0</v>
       </c>
-      <c r="F8" s="10" t="n">
+      <c r="F8" s="10">
         <v>239</v>
       </c>
-      <c r="G8" s="10" t="n">
+      <c r="G8" s="10">
         <v>0</v>
       </c>
-      <c r="H8" s="14" t="inlineStr">
-        <is>
-          <t>kPa</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>DF_robot</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>air_val_min</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Air value (minimum)</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Air value: raw reading in open air</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="n">
+      <c r="H8" s="14" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E9" s="3">
         <v>0</v>
       </c>
-      <c r="F9" s="3" t="n">
+      <c r="F9" s="3">
         <v>0</v>
       </c>
-      <c r="G9" s="3" t="n">
+      <c r="G9" s="3">
         <v>0</v>
       </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>ADC</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>DF_robot</t>
-        </is>
-      </c>
-      <c r="B10" s="15" t="inlineStr">
-        <is>
-          <t>air_val_max</t>
-        </is>
-      </c>
-      <c r="C10" s="15" t="inlineStr">
-        <is>
-          <t>Air value (max)</t>
-        </is>
-      </c>
-      <c r="D10" s="15" t="inlineStr">
-        <is>
-          <t>Air value: raw reading in open air</t>
-        </is>
-      </c>
-      <c r="E10" s="15" t="n">
+      <c r="H9" s="5" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="E10" s="15">
         <v>0</v>
       </c>
-      <c r="F10" s="15" t="n">
+      <c r="F10" s="15">
         <v>1023</v>
       </c>
-      <c r="G10" s="15" t="n">
+      <c r="G10" s="15">
         <v>590</v>
       </c>
-      <c r="H10" s="14" t="inlineStr">
-        <is>
-          <t>ADC</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>DF_robot</t>
-        </is>
-      </c>
-      <c r="B11" s="28" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="C11" s="28" t="inlineStr">
-        <is>
-          <t>Upper threshold</t>
-        </is>
-      </c>
-      <c r="D11" s="28" t="inlineStr">
-        <is>
-          <t>The upper threshold used to calculate the state of the sensor.</t>
-        </is>
-      </c>
-      <c r="E11" s="28" t="n">
+      <c r="H10" s="14" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="E11" s="19">
         <v>0</v>
       </c>
-      <c r="F11" s="28" t="n">
+      <c r="F11" s="19">
         <v>1023</v>
       </c>
-      <c r="G11" s="28" t="n">
+      <c r="G11" s="19">
         <v>450</v>
       </c>
-      <c r="H11" s="20" t="inlineStr">
-        <is>
-          <t>ADC</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>DF_robot</t>
-        </is>
-      </c>
-      <c r="B12" s="28" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
-      <c r="C12" s="28" t="inlineStr">
-        <is>
-          <t>Lower threshold</t>
-        </is>
-      </c>
-      <c r="D12" s="28" t="inlineStr">
-        <is>
-          <t>The lower theshold used to calculate the state of the sensor.</t>
-        </is>
-      </c>
-      <c r="E12" s="28" t="n">
+      <c r="H11" s="20" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="15" customHeight="1">
+      <c r="A12" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="E12" s="19">
         <v>0</v>
       </c>
-      <c r="F12" s="28" t="n">
+      <c r="F12" s="19">
         <v>1023</v>
       </c>
-      <c r="G12" s="28" t="n">
+      <c r="G12" s="19">
         <v>350</v>
       </c>
-      <c r="H12" s="20" t="inlineStr">
-        <is>
-          <t>ADC</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>DF_robot</t>
-        </is>
-      </c>
-      <c r="B13" s="28" t="inlineStr">
-        <is>
-          <t>shallow</t>
-        </is>
-      </c>
-      <c r="C13" s="28" t="inlineStr">
-        <is>
-          <t>Shallow sensor depth</t>
-        </is>
-      </c>
-      <c r="D13" s="28" t="inlineStr">
-        <is>
-          <t>The depth of the sensor closest to the surface.</t>
-        </is>
-      </c>
-      <c r="E13" s="28" t="n">
+      <c r="H12" s="20" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="15" customHeight="1">
+      <c r="A13" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="E13" s="19">
         <v>0</v>
       </c>
-      <c r="F13" s="28" t="n">
+      <c r="F13" s="19">
         <v>200</v>
       </c>
-      <c r="G13" s="28" t="n">
+      <c r="G13" s="19">
         <v>15</v>
       </c>
-      <c r="H13" s="20" t="inlineStr">
-        <is>
-          <t>cm</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>DF_robot</t>
-        </is>
-      </c>
-      <c r="B14" s="28" t="inlineStr">
-        <is>
-          <t>deep</t>
-        </is>
-      </c>
-      <c r="C14" s="28" t="inlineStr">
-        <is>
-          <t>Deep sensor depth</t>
-        </is>
-      </c>
-      <c r="D14" s="28" t="inlineStr">
-        <is>
-          <t>The depth of the sensor deepest in the soil.</t>
-        </is>
-      </c>
-      <c r="E14" s="28" t="n">
+      <c r="H13" s="20" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="15" customHeight="1">
+      <c r="A14" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="E14" s="19">
         <v>0</v>
       </c>
-      <c r="F14" s="28" t="n">
+      <c r="F14" s="19">
         <v>200</v>
       </c>
-      <c r="G14" s="28" t="n">
+      <c r="G14" s="19">
         <v>40</v>
       </c>
-      <c r="H14" s="20" t="inlineStr">
-        <is>
-          <t>cm</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>DF_robot</t>
-        </is>
-      </c>
-      <c r="B15" s="28" t="inlineStr">
-        <is>
-          <t>threshold</t>
-        </is>
-      </c>
-      <c r="C15" s="28" t="inlineStr">
-        <is>
-          <t>Front arrival reading</t>
-        </is>
-      </c>
-      <c r="D15" s="28" t="inlineStr">
-        <is>
-          <t>The threshold for the front arrival.</t>
-        </is>
-      </c>
-      <c r="E15" s="28" t="n">
+      <c r="H14" s="20" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="15" customHeight="1">
+      <c r="A15" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="E15" s="19">
         <v>0</v>
       </c>
-      <c r="F15" s="28" t="n">
+      <c r="F15" s="19">
         <v>1023</v>
       </c>
-      <c r="G15" s="28" t="n">
+      <c r="G15" s="19">
         <v>400</v>
       </c>
-      <c r="H15" s="14" t="inlineStr">
-        <is>
-          <t>ADC</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>Watermark</t>
-        </is>
-      </c>
-      <c r="B16" s="28" t="inlineStr">
-        <is>
-          <t>air_val_max</t>
-        </is>
-      </c>
-      <c r="C16" s="28" t="inlineStr">
-        <is>
-          <t>Air value (max)</t>
-        </is>
-      </c>
-      <c r="D16" s="28" t="inlineStr">
-        <is>
-          <t>The maximum air value.</t>
-        </is>
-      </c>
-      <c r="E16" s="28" t="n">
+      <c r="H15" s="14" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="15" customHeight="1">
+      <c r="A16" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="E16" s="19">
         <v>0</v>
       </c>
-      <c r="F16" s="28" t="n">
+      <c r="F16" s="19">
         <v>239</v>
       </c>
-      <c r="G16" s="28" t="n">
+      <c r="G16" s="19">
         <v>239</v>
       </c>
-      <c r="H16" s="14" t="inlineStr">
-        <is>
-          <t>kPa</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>Watermark_Temperature</t>
-        </is>
-      </c>
-      <c r="B17" s="28" t="inlineStr">
-        <is>
-          <t>air_val_max</t>
-        </is>
-      </c>
-      <c r="C17" s="28" t="inlineStr">
-        <is>
-          <t>Air value (max)</t>
-        </is>
-      </c>
-      <c r="D17" s="28" t="inlineStr">
-        <is>
-          <t>The maximum air value.</t>
-        </is>
-      </c>
-      <c r="E17" s="28" t="n">
+      <c r="H16" s="14" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="15" customHeight="1">
+      <c r="A17" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="D17" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="E17" s="19">
         <v>0</v>
       </c>
-      <c r="F17" s="28" t="n">
+      <c r="F17" s="19">
         <v>239</v>
       </c>
-      <c r="G17" s="28" t="n">
+      <c r="G17" s="19">
         <v>239</v>
       </c>
-      <c r="H17" s="14" t="inlineStr">
-        <is>
-          <t>kPa</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>Watermark_Temperature</t>
-        </is>
-      </c>
-      <c r="B18" s="28" t="inlineStr">
-        <is>
-          <t>water_val</t>
-        </is>
-      </c>
-      <c r="C18" s="28" t="inlineStr">
-        <is>
-          <t>Water value</t>
-        </is>
-      </c>
-      <c r="D18" s="28" t="inlineStr">
-        <is>
-          <t>The set water value.</t>
-        </is>
-      </c>
-      <c r="E18" s="28" t="n">
+      <c r="H17" s="14" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="15" customHeight="1">
+      <c r="A18" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="B18" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="D18" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="E18" s="19">
         <v>0</v>
       </c>
-      <c r="F18" s="28" t="n">
+      <c r="F18" s="19">
         <v>239</v>
       </c>
-      <c r="G18" s="28" t="n">
+      <c r="G18" s="19">
         <v>0</v>
       </c>
-      <c r="H18" s="14" t="inlineStr">
-        <is>
-          <t>kPa</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>Watermark</t>
-        </is>
-      </c>
-      <c r="B19" s="28" t="inlineStr">
-        <is>
-          <t>soil_type</t>
-        </is>
-      </c>
-      <c r="C19" s="28" t="inlineStr">
-        <is>
-          <t>Soil Type</t>
-        </is>
-      </c>
-      <c r="D19" s="21" t="inlineStr">
-        <is>
-          <t>Soil texture sets the irrigation thresholds. Choosing a type fills in the two tension values below, which you can still adjust.</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>Loam</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Loamy sand|Fine sandy loam|Sandy loam|Loam|Clay</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>Watermark_Temperature</t>
-        </is>
-      </c>
-      <c r="B20" s="28" t="inlineStr">
-        <is>
-          <t>soil_type</t>
-        </is>
-      </c>
-      <c r="C20" s="28" t="inlineStr">
-        <is>
-          <t>Soil Type</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>Soil texture sets the irrigation thresholds. Choosing a type fills in the two tension values below, which you can still adjust.</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>Loam</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Loamy sand|Fine sandy loam|Sandy loam|Loam|Clay</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="10" t="inlineStr">
-        <is>
-          <t>Watermark</t>
-        </is>
-      </c>
-      <c r="B21" s="28" t="inlineStr">
-        <is>
-          <t>thr_low</t>
-        </is>
-      </c>
-      <c r="C21" s="21" t="inlineStr">
-        <is>
-          <t>Wet threshold (10% depletion)</t>
-        </is>
-      </c>
-      <c r="D21" s="29" t="inlineStr">
-        <is>
-          <t>Threshold to calculate how wet the soil is at 10% depletion.</t>
-        </is>
-      </c>
-      <c r="E21" s="29" t="n">
+      <c r="H18" s="14" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="15" customHeight="1">
+      <c r="A19" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="B19" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="D19" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="I19" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="15" customHeight="1">
+      <c r="A20" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="I20" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A21" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="B21" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="C21" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E21" s="16">
         <v>0</v>
       </c>
-      <c r="F21" s="29" t="n">
+      <c r="F21" s="16">
         <v>239</v>
       </c>
-      <c r="G21" s="29" t="n">
+      <c r="G21" s="16">
         <v>23</v>
       </c>
-      <c r="H21" s="14" t="inlineStr">
-        <is>
-          <t>kPa</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>Watermark</t>
-        </is>
-      </c>
-      <c r="B22" s="28" t="inlineStr">
-        <is>
-          <t>thr_high</t>
-        </is>
-      </c>
-      <c r="C22" s="29" t="inlineStr">
-        <is>
-          <t>Dry threshold (40% depletion)</t>
-        </is>
-      </c>
-      <c r="D22" s="29" t="inlineStr">
-        <is>
-          <t>Threshold to calculate how dry the soil is at 40% depletion.</t>
-        </is>
-      </c>
-      <c r="E22" s="29" t="n">
+      <c r="H21" s="14" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A22" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="B22" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="E22" s="16">
         <v>0</v>
       </c>
-      <c r="F22" s="29" t="n">
+      <c r="F22" s="16">
         <v>239</v>
       </c>
-      <c r="G22" s="29" t="n">
+      <c r="G22" s="16">
         <v>65</v>
       </c>
-      <c r="H22" s="14" t="inlineStr">
-        <is>
-          <t>kPa</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>Watermark_Temperature</t>
-        </is>
-      </c>
-      <c r="B23" s="28" t="inlineStr">
-        <is>
-          <t>thr_low</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Wet threshold (10% depletion)</t>
-        </is>
-      </c>
-      <c r="D23" s="29" t="inlineStr">
-        <is>
-          <t>Threshold to calculate how wet the soil is at 10% depletion.</t>
-        </is>
-      </c>
-      <c r="E23" s="29" t="n">
+      <c r="H22" s="14" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A23" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="C23" t="s">
+        <v>143</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E23" s="16">
         <v>0</v>
       </c>
-      <c r="F23" s="29" t="n">
+      <c r="F23" s="16">
         <v>239</v>
       </c>
-      <c r="G23" s="29" t="n">
+      <c r="G23" s="16">
         <v>23</v>
       </c>
-      <c r="H23" s="14" t="inlineStr">
-        <is>
-          <t>kPa</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t>Watermark_Temperature</t>
-        </is>
-      </c>
-      <c r="B24" s="28" t="inlineStr">
-        <is>
-          <t>thr_high</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Dry threshold (40% depletion)</t>
-        </is>
-      </c>
-      <c r="D24" s="29" t="inlineStr">
-        <is>
-          <t>Threshold to calculate how dry the soil is at 40% depletion.</t>
-        </is>
-      </c>
-      <c r="E24" s="29" t="n">
+      <c r="H23" s="14" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A24" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="C24" t="s">
+        <v>145</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="E24" s="16">
         <v>0</v>
       </c>
-      <c r="F24" s="29" t="n">
+      <c r="F24" s="16">
         <v>239</v>
       </c>
-      <c r="G24" s="29" t="n">
+      <c r="G24" s="16">
         <v>65</v>
       </c>
-      <c r="H24" s="14" t="inlineStr">
-        <is>
-          <t>kPa</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Watermark</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>wiring</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Connection</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>How the sensor reaches the board. Through the 200SS-VA3 adapter, which does the excitation and calibration itself, or wired straight to the Arduino with a series resistor. Direct wiring supports one Watermark only: two bare sensors in the same soil read through each other and damage their electrodes.</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>200SS-VA3 adapter</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>200SS-VA3 adapter|Direct to Arduino</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Watermark</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Rx</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Series resistor</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Series resistor between the sensor and ground, used only for direct wiring. Irrometer's reference circuit uses 10 kilohms.</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
+      <c r="H24" s="14" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A25" t="s">
+        <v>120</v>
+      </c>
+      <c r="B25" t="s">
+        <v>147</v>
+      </c>
+      <c r="C25" t="s">
+        <v>148</v>
+      </c>
+      <c r="D25" t="s">
+        <v>149</v>
+      </c>
+      <c r="G25" t="s">
+        <v>150</v>
+      </c>
+      <c r="I25" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A26" t="s">
+        <v>120</v>
+      </c>
+      <c r="B26" t="s">
+        <v>152</v>
+      </c>
+      <c r="C26" t="s">
+        <v>153</v>
+      </c>
+      <c r="D26" t="s">
+        <v>154</v>
+      </c>
+      <c r="E26">
         <v>1</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F26">
         <v>100</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G26">
         <v>10</v>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>kOhm</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Temperature</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>wiring</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Connection</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>How the sensor reaches the board. Through the 200SS-VA3 adapter, which does the excitation and calibration itself, or wired straight to the Arduino with a series resistor. Direct wiring supports one Watermark only: two bare sensors in the same soil read through each other and damage their electrodes.</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>200SS-VA3 adapter</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>200SS-VA3 adapter|Direct to Arduino</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Temperature</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Rx</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Series resistor</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Series resistor between the sensor and ground, used only for direct wiring. Irrometer's reference circuit uses 10 kilohms.</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
+      <c r="H26" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A27" t="s">
+        <v>156</v>
+      </c>
+      <c r="B27" t="s">
+        <v>147</v>
+      </c>
+      <c r="C27" t="s">
+        <v>148</v>
+      </c>
+      <c r="D27" t="s">
+        <v>149</v>
+      </c>
+      <c r="G27" t="s">
+        <v>150</v>
+      </c>
+      <c r="I27" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A28" t="s">
+        <v>156</v>
+      </c>
+      <c r="B28" t="s">
+        <v>152</v>
+      </c>
+      <c r="C28" t="s">
+        <v>153</v>
+      </c>
+      <c r="D28" t="s">
+        <v>154</v>
+      </c>
+      <c r="E28">
         <v>1</v>
       </c>
-      <c r="F28" t="n">
+      <c r="F28">
         <v>100</v>
       </c>
-      <c r="G28" t="n">
+      <c r="G28">
         <v>10</v>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>kOhm</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Watermark</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>soil_temp_c</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Soil temperature</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>Soil temperature used to compensate the Watermark calibration when wiring direct. Irrometer uses 24 C when no temperature sensor is available.</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
+      <c r="H28" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A29" t="s">
+        <v>120</v>
+      </c>
+      <c r="B29" t="s">
+        <v>157</v>
+      </c>
+      <c r="C29" t="s">
+        <v>158</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="E29">
         <v>-10</v>
       </c>
-      <c r="F29" t="n">
+      <c r="F29">
         <v>60</v>
       </c>
-      <c r="G29" t="n">
+      <c r="G29">
         <v>24</v>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Temperature</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>therm_r25</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>Thermistor R at 25 C</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>Resistance of the 200TS at 25 C, for direct wiring. NOT PUBLISHED BY IRROMETER: the datasheet says the curve is built into their reading devices. The default assumes a generic 10 kilohm NTC and must be checked against your sensor before the reading is trusted.</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
+      <c r="H29" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A30" t="s">
+        <v>156</v>
+      </c>
+      <c r="B30" t="s">
+        <v>161</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="E30">
         <v>100</v>
       </c>
-      <c r="F30" t="n">
+      <c r="F30">
         <v>100000</v>
       </c>
-      <c r="G30" t="n">
+      <c r="G30">
         <v>10000</v>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Ohm</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Temperature</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>therm_beta</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Thermistor beta</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>Beta coefficient of the 200TS, for direct wiring. Same caveat as the resistance above: this is a generic NTC value, not an Irrometer figure.</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
+      <c r="H30" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A31" t="s">
+        <v>156</v>
+      </c>
+      <c r="B31" t="s">
+        <v>165</v>
+      </c>
+      <c r="C31" t="s">
+        <v>166</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E31">
         <v>1000</v>
       </c>
-      <c r="F31" t="n">
+      <c r="F31">
         <v>6000</v>
       </c>
-      <c r="G31" t="n">
+      <c r="G31">
         <v>3435</v>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="15.75" customHeight="1"/>
+      <c r="H31" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="15.75" customHeight="1"/>
     <row r="33" ht="15.75" customHeight="1"/>
     <row r="34" ht="15.75" customHeight="1"/>
     <row r="35" ht="15.75" customHeight="1"/>
@@ -4586,182 +4658,118 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:E1000"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="46" customWidth="1" min="5" max="5"/>
-    <col width="8.83203125" customWidth="1" min="6" max="26"/>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="5" max="5" width="46" customWidth="1"/>
+    <col min="6" max="26" width="8.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>question_key</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>question_label</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>required (TRUE/FALSE)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>options / placeholder</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>filename</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>File name</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>e.g. apples_field2 (no spaces, no .ino)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Your name</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>e.g. John R.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>country</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Country</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>e.g. United States of America</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Email address</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>e.g. name@example.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>ino_comment</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Comment to include in the code (optional)</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>e.g. Orchard block 2, installed June 2026</t>
-        </is>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -5751,354 +5759,236 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C19"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:C1000"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="8.83203125" customWidth="1" min="3" max="26"/>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="26" width="8.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>port_value</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>port_tip</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>active (TRUE/FALSE)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>A1</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Analog pin A1. A0 is taken by the shield's buttons, so sensors start here.</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>A2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Analog pin A2.</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A3</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Analog pin A3.</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A4</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Analog pin A4.</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A5</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Analog pin A5.</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>D1</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Digital pin 1.</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>D2</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Digital pin 2.</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Digital pin 3. </t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>D4</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>Digital pin 4.</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>D5</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Digital pin 5. </t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>D6</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Digital pin 6. </t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>D7</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Digital pin 7. </t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>D8</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Digital pin 8. </t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>D9</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Digital pin 9. </t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>D10</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>Digital pin 10.</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>D11</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>Digital pin 11.</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>D12</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Digital pin 12. </t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>D13</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>Digital pin 13.</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1"/>
-    <row r="22" ht="15.75" customHeight="1"/>
-    <row r="23" ht="15.75" customHeight="1"/>
-    <row r="24" ht="15.75" customHeight="1"/>
-    <row r="25" ht="15.75" customHeight="1"/>
-    <row r="26" ht="15.75" customHeight="1"/>
-    <row r="27" ht="15.75" customHeight="1"/>
-    <row r="28" ht="15.75" customHeight="1"/>
-    <row r="29" ht="15.75" customHeight="1"/>
-    <row r="30" ht="15.75" customHeight="1"/>
-    <row r="31" ht="15.75" customHeight="1"/>
-    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C1" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B3" t="s">
+        <v>198</v>
+      </c>
+      <c r="C3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B4" t="s">
+        <v>200</v>
+      </c>
+      <c r="C4" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>201</v>
+      </c>
+      <c r="B5" t="s">
+        <v>202</v>
+      </c>
+      <c r="C5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>203</v>
+      </c>
+      <c r="B6" t="s">
+        <v>204</v>
+      </c>
+      <c r="C6" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>205</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="C7" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>207</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="C8" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>209</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="C9" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>211</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="C10" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>213</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="C11" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>215</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="C12" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>217</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="C13" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>219</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="C14" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>221</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="C15" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>223</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="C16" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>225</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="C17" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>227</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="C18" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>229</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="C19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="22" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="23" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="24" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="25" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="26" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="27" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="28" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="29" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="30" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="31" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="32" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="33" ht="15.75" customHeight="1"/>
     <row r="34" ht="15.75" customHeight="1"/>
     <row r="35" ht="15.75" customHeight="1"/>
@@ -7074,270 +6964,180 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D12"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:D1000"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="8.83203125" customWidth="1" min="5" max="26"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="50" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="5" max="26" width="8.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>viz_key</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>label</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>viz_tip</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>active (TRUE/FALSE)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>No visualization</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>Display the information in a visual representation on the LCD screen. Currently there is nothing selected.</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>bar</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Loading bar</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Displays a loading bar that changes based on water content.</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>raw_lcd</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Raw value</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Displays the raw sensor value</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>state_lcd</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>State: Very Dry, Dry, or Wet</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Displays the general state at which soil seems to be for the capacitive sensors</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>transformed_lcd</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Transformed Raw Value 0-100</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>A more concise version of the raw sensor value</t>
-        </is>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>246</v>
       </c>
       <c r="D6" s="3" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>rate</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Rate of change (future)</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>The change in available water over time</t>
-        </is>
+    <row r="7" spans="1:4">
+      <c r="A7" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>249</v>
       </c>
       <c r="D7" s="3" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>front_lcd</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>Front detected</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>Shows front detected when the wetting front reaches the deep sensor</t>
-        </is>
+    <row r="8" spans="1:4">
+      <c r="A8" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>251</v>
       </c>
       <c r="D8" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>temp_lcd</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>Temperature</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>Displays the temperatue in celsius</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TRUE </t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>kpa_lcd</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>Tension</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>Displays soil tension in kPa</t>
-        </is>
-      </c>
-      <c r="D10" s="29" t="b">
+    <row r="9" spans="1:4">
+      <c r="A9" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="D10" s="16" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>rate_lcd</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>Flow rate</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>Displays the flow rate between 2 sensors</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TRUE </t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>wm_state_lcd</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>State: Dry plant stressed, Irrigation range, or Saturation</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>Displays the state at which the soils seems to be for the Watermark sensors</t>
-        </is>
+    <row r="11" spans="1:4" ht="15" customHeight="1">
+      <c r="A11" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="15" customHeight="1">
+      <c r="A12" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>258</v>
       </c>
       <c r="D12" t="b">
         <v>1</v>

--- a/data/sensor_configuration_v2.xlsx
+++ b/data/sensor_configuration_v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fernandolaguna/Desktop/Low-Cost-Water-Tech/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE5DCCCB-5358-2D4C-B25D-14E28B468320}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C02482C7-CBB6-BC4C-A700-02C4A10995BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="17400" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="17400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sensors" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="260">
   <si>
     <t>sensor_name</t>
   </si>
@@ -801,6 +801,9 @@
   </si>
   <si>
     <t>Displays the state at which the soils seems to be for the Watermark sensors</t>
+  </si>
+  <si>
+    <t>The downward movement of water infiltrating through the soil.</t>
   </si>
 </sst>
 </file>
@@ -1549,7 +1552,9 @@
         <v>59</v>
       </c>
       <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
+      <c r="D9" s="3" t="s">
+        <v>259</v>
+      </c>
       <c r="E9" s="3" t="s">
         <v>37</v>
       </c>
